--- a/EpiRank_改/ERA_result_seqday_d_0.95_loops_305.xlsx
+++ b/EpiRank_改/ERA_result_seqday_d_0.95_loops_305.xlsx
@@ -714,10 +714,10 @@
         <v>0.012835</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA2" s="3" t="n">
         <v>9</v>
@@ -1179,10 +1179,10 @@
         <v>0.012838</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA5" s="3" t="n">
         <v>11</v>
@@ -1938,10 +1938,10 @@
         <v>0.011997</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA10" s="3" t="n">
         <v>4</v>
@@ -2093,10 +2093,10 @@
         <v>0.016941</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA11" s="3" t="n">
         <v>8</v>
@@ -2403,10 +2403,10 @@
         <v>0.004698</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA13" s="3" t="n">
         <v>4</v>
@@ -3708,7 +3708,7 @@
         <v>0.004713</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z22" s="3" t="n">
         <v>0</v>
@@ -4098,10 +4098,10 @@
         <v>0.011024</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA25" s="3" t="n">
         <v>8</v>
@@ -4488,7 +4488,7 @@
         <v>0.007023</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z28" s="3" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0.009729</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA32" s="3" t="n">
         <v>24</v>
@@ -5348,10 +5348,10 @@
         <v>0.008265</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA35" s="3" t="n">
         <v>5</v>
@@ -6188,10 +6188,10 @@
         <v>0.01038</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z42" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA42" s="3" t="n">
         <v>0</v>
@@ -7028,7 +7028,7 @@
         <v>0.006149</v>
       </c>
       <c r="Y49" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z49" s="3" t="n">
         <v>0</v>
@@ -7148,7 +7148,7 @@
         <v>0.004587</v>
       </c>
       <c r="Y50" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z50" s="3" t="n">
         <v>-0</v>
@@ -7628,10 +7628,10 @@
         <v>0.0015</v>
       </c>
       <c r="Y54" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z54" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA54" s="3" t="n">
         <v>35</v>
@@ -7988,7 +7988,7 @@
         <v>0.005555</v>
       </c>
       <c r="Y57" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z57" s="3" t="n">
         <v>0</v>
@@ -8588,10 +8588,10 @@
         <v>0.002648</v>
       </c>
       <c r="Y62" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z62" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA62" s="3" t="n">
         <v>4</v>
@@ -9551,7 +9551,7 @@
         <v>0</v>
       </c>
       <c r="Z70" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA70" s="3" t="n">
         <v>6</v>
@@ -9658,7 +9658,7 @@
         <v>0.002491</v>
       </c>
       <c r="Y71" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z71" s="3" t="n">
         <v>-0</v>
@@ -9988,10 +9988,10 @@
         <v>0.002616</v>
       </c>
       <c r="Y74" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z74" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA74" s="3" t="n">
         <v>2</v>
@@ -10098,10 +10098,10 @@
         <v>0.006096</v>
       </c>
       <c r="Y75" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z75" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA75" s="3" t="n">
         <v>1</v>
@@ -10651,7 +10651,7 @@
         <v>0</v>
       </c>
       <c r="Z80" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA80" s="3" t="n">
         <v>4</v>
@@ -10758,10 +10758,10 @@
         <v>0.003248</v>
       </c>
       <c r="Y81" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z81" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA81" s="3" t="n">
         <v>3</v>
@@ -11088,7 +11088,7 @@
         <v>0.002498</v>
       </c>
       <c r="Y84" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z84" s="3" t="n">
         <v>-0</v>
@@ -11858,7 +11858,7 @@
         <v>0.002613</v>
       </c>
       <c r="Y91" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z91" s="3" t="n">
         <v>-0</v>
@@ -12188,10 +12188,10 @@
         <v>0.002947</v>
       </c>
       <c r="Y94" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z94" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA94" s="3" t="n">
         <v>3</v>
@@ -12518,10 +12518,10 @@
         <v>0.002789</v>
       </c>
       <c r="Y97" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z97" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA97" s="3" t="n">
         <v>1</v>
@@ -12628,10 +12628,10 @@
         <v>0.003197</v>
       </c>
       <c r="Y98" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z98" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA98" s="3" t="n">
         <v>1</v>
@@ -13288,10 +13288,10 @@
         <v>0.003369</v>
       </c>
       <c r="Y104" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z104" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA104" s="3" t="n">
         <v>2</v>
@@ -13728,10 +13728,10 @@
         <v>0.003716</v>
       </c>
       <c r="Y108" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z108" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA108" s="3" t="n">
         <v>0</v>
@@ -14058,10 +14058,10 @@
         <v>0.002802</v>
       </c>
       <c r="Y111" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z111" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA111" s="3" t="n">
         <v>0</v>
@@ -14168,10 +14168,10 @@
         <v>0.003672</v>
       </c>
       <c r="Y112" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z112" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA112" s="3" t="n">
         <v>0</v>
@@ -14391,7 +14391,7 @@
         <v>0</v>
       </c>
       <c r="Z114" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA114" s="3" t="n">
         <v>1</v>
@@ -14501,7 +14501,7 @@
         <v>0</v>
       </c>
       <c r="Z115" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA115" s="3" t="n">
         <v>0</v>
@@ -14608,10 +14608,10 @@
         <v>0.002715</v>
       </c>
       <c r="Y116" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z116" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA116" s="3" t="n">
         <v>1</v>
@@ -14718,10 +14718,10 @@
         <v>0.0059</v>
       </c>
       <c r="Y117" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z117" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA117" s="3" t="n">
         <v>0</v>
@@ -14938,10 +14938,10 @@
         <v>0.002833</v>
       </c>
       <c r="Y119" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z119" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA119" s="3" t="n">
         <v>1</v>
@@ -15051,7 +15051,7 @@
         <v>0</v>
       </c>
       <c r="Z120" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA120" s="3" t="n">
         <v>0</v>
@@ -15158,10 +15158,10 @@
         <v>0.001286</v>
       </c>
       <c r="Y121" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z121" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA121" s="3" t="n">
         <v>1</v>
@@ -15378,10 +15378,10 @@
         <v>0.00191</v>
       </c>
       <c r="Y123" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z123" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA123" s="3" t="n">
         <v>1</v>
@@ -15488,10 +15488,10 @@
         <v>0.001759</v>
       </c>
       <c r="Y124" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z124" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA124" s="3" t="n">
         <v>1</v>
@@ -16368,10 +16368,10 @@
         <v>0.002787</v>
       </c>
       <c r="Y132" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z132" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA132" s="3" t="n">
         <v>2</v>
@@ -16481,7 +16481,7 @@
         <v>-0</v>
       </c>
       <c r="Z133" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA133" s="3" t="n">
         <v>0</v>
@@ -16588,10 +16588,10 @@
         <v>0.003344</v>
       </c>
       <c r="Y134" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z134" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA134" s="3" t="n">
         <v>3</v>
@@ -16698,10 +16698,10 @@
         <v>0.002116</v>
       </c>
       <c r="Y135" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z135" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA135" s="3" t="n">
         <v>0</v>
@@ -16808,10 +16808,10 @@
         <v>0.002579</v>
       </c>
       <c r="Y136" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z136" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA136" s="3" t="n">
         <v>0</v>
@@ -16918,10 +16918,10 @@
         <v>0.002381</v>
       </c>
       <c r="Y137" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z137" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA137" s="3" t="n">
         <v>2</v>
@@ -17031,7 +17031,7 @@
         <v>0</v>
       </c>
       <c r="Z138" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA138" s="3" t="n">
         <v>0</v>
@@ -17361,7 +17361,7 @@
         <v>0</v>
       </c>
       <c r="Z141" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA141" s="3" t="n">
         <v>0</v>
@@ -17578,10 +17578,10 @@
         <v>0.00181</v>
       </c>
       <c r="Y143" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z143" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA143" s="3" t="n">
         <v>1</v>
@@ -18128,10 +18128,10 @@
         <v>0.002964</v>
       </c>
       <c r="Y148" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z148" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA148" s="3" t="n">
         <v>3</v>
@@ -18898,10 +18898,10 @@
         <v>0.001295</v>
       </c>
       <c r="Y155" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z155" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA155" s="3" t="n">
         <v>0</v>
@@ -19118,10 +19118,10 @@
         <v>0.002604</v>
       </c>
       <c r="Y157" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z157" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA157" s="3" t="n">
         <v>7</v>
@@ -19338,10 +19338,10 @@
         <v>0.002147</v>
       </c>
       <c r="Y159" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z159" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA159" s="3" t="n">
         <v>1</v>
@@ -19448,10 +19448,10 @@
         <v>0.002491</v>
       </c>
       <c r="Y160" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z160" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA160" s="3" t="n">
         <v>2</v>
@@ -19671,7 +19671,7 @@
         <v>0</v>
       </c>
       <c r="Z162" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA162" s="3" t="n">
         <v>1</v>
@@ -19998,10 +19998,10 @@
         <v>0.001901</v>
       </c>
       <c r="Y165" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z165" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA165" s="3" t="n">
         <v>0</v>
@@ -20218,10 +20218,10 @@
         <v>0.001621</v>
       </c>
       <c r="Y167" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z167" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA167" s="3" t="n">
         <v>2</v>
@@ -20551,7 +20551,7 @@
         <v>-0</v>
       </c>
       <c r="Z170" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA170" s="3" t="n">
         <v>5</v>
@@ -20771,7 +20771,7 @@
         <v>-0</v>
       </c>
       <c r="Z172" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA172" s="3" t="n">
         <v>1</v>
@@ -20988,10 +20988,10 @@
         <v>0.002004</v>
       </c>
       <c r="Y174" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z174" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA174" s="3" t="n">
         <v>2</v>
@@ -21321,7 +21321,7 @@
         <v>0</v>
       </c>
       <c r="Z177" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA177" s="3" t="n">
         <v>2</v>
@@ -21431,7 +21431,7 @@
         <v>0</v>
       </c>
       <c r="Z178" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA178" s="3" t="n">
         <v>0</v>
@@ -21648,10 +21648,10 @@
         <v>0.001235</v>
       </c>
       <c r="Y180" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z180" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA180" s="3" t="n">
         <v>1</v>
@@ -21758,7 +21758,7 @@
         <v>0.0009700000000000001</v>
       </c>
       <c r="Y181" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z181" s="3" t="n">
         <v>0</v>
@@ -21868,10 +21868,10 @@
         <v>0.001797</v>
       </c>
       <c r="Y182" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z182" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA182" s="3" t="n">
         <v>0</v>
@@ -22091,7 +22091,7 @@
         <v>0</v>
       </c>
       <c r="Z184" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA184" s="3" t="n">
         <v>2</v>
@@ -22528,10 +22528,10 @@
         <v>0.001192</v>
       </c>
       <c r="Y188" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z188" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA188" s="3" t="n">
         <v>0</v>
@@ -22748,10 +22748,10 @@
         <v>0.002542</v>
       </c>
       <c r="Y190" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z190" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA190" s="3" t="n">
         <v>1</v>
@@ -22861,7 +22861,7 @@
         <v>-0</v>
       </c>
       <c r="Z191" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA191" s="3" t="n">
         <v>0</v>
@@ -22968,10 +22968,10 @@
         <v>0.001259</v>
       </c>
       <c r="Y192" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z192" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA192" s="3" t="n">
         <v>1</v>
@@ -23518,10 +23518,10 @@
         <v>0.002087</v>
       </c>
       <c r="Y197" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z197" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA197" s="3" t="n">
         <v>0</v>
@@ -23628,7 +23628,7 @@
         <v>0.001081</v>
       </c>
       <c r="Y198" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z198" s="3" t="n">
         <v>-0</v>
@@ -23738,10 +23738,10 @@
         <v>0.001708</v>
       </c>
       <c r="Y199" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z199" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA199" s="3" t="n">
         <v>0</v>
@@ -23851,7 +23851,7 @@
         <v>0</v>
       </c>
       <c r="Z200" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA200" s="3" t="n">
         <v>0</v>
@@ -24178,10 +24178,10 @@
         <v>0.001669</v>
       </c>
       <c r="Y203" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z203" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA203" s="3" t="n">
         <v>0</v>
@@ -24511,7 +24511,7 @@
         <v>0</v>
       </c>
       <c r="Z206" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA206" s="3" t="n">
         <v>1</v>
@@ -24621,7 +24621,7 @@
         <v>0</v>
       </c>
       <c r="Z207" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA207" s="3" t="n">
         <v>3</v>
@@ -24728,7 +24728,7 @@
         <v>0.001245</v>
       </c>
       <c r="Y208" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z208" s="3" t="n">
         <v>0</v>
@@ -25058,10 +25058,10 @@
         <v>0.0008140000000000001</v>
       </c>
       <c r="Y211" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z211" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA211" s="3" t="n">
         <v>0</v>
@@ -25168,7 +25168,7 @@
         <v>0.001943</v>
       </c>
       <c r="Y212" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z212" s="3" t="n">
         <v>0</v>
@@ -25608,10 +25608,10 @@
         <v>0.001782</v>
       </c>
       <c r="Y216" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z216" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA216" s="3" t="n">
         <v>2</v>
@@ -25941,7 +25941,7 @@
         <v>0</v>
       </c>
       <c r="Z219" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA219" s="3" t="n">
         <v>0</v>
@@ -26268,7 +26268,7 @@
         <v>0.001</v>
       </c>
       <c r="Y222" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z222" s="3" t="n">
         <v>0</v>
@@ -26488,10 +26488,10 @@
         <v>0.002084</v>
       </c>
       <c r="Y224" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z224" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA224" s="3" t="n">
         <v>2</v>
@@ -26688,7 +26688,7 @@
         <v>0.00125</v>
       </c>
       <c r="Y226" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z226" s="3" t="n">
         <v>-0</v>
@@ -26788,7 +26788,7 @@
         <v>0.000905</v>
       </c>
       <c r="Y227" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z227" s="3" t="n">
         <v>-0</v>
@@ -27088,10 +27088,10 @@
         <v>0.000867</v>
       </c>
       <c r="Y230" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z230" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA230" s="3" t="n">
         <v>0</v>
@@ -27191,7 +27191,7 @@
         <v>0</v>
       </c>
       <c r="Z231" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA231" s="3" t="n">
         <v>0</v>
@@ -27388,7 +27388,7 @@
         <v>0.001386</v>
       </c>
       <c r="Y233" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z233" s="3" t="n">
         <v>-0</v>
@@ -27788,10 +27788,10 @@
         <v>0.000672</v>
       </c>
       <c r="Y237" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z237" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA237" s="3" t="n">
         <v>2</v>
@@ -27888,10 +27888,10 @@
         <v>0.001309</v>
       </c>
       <c r="Y238" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z238" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA238" s="3" t="n">
         <v>0</v>
@@ -27991,7 +27991,7 @@
         <v>0</v>
       </c>
       <c r="Z239" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA239" s="3" t="n">
         <v>1</v>
@@ -28091,7 +28091,7 @@
         <v>0</v>
       </c>
       <c r="Z240" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA240" s="3" t="n">
         <v>0</v>
@@ -28288,10 +28288,10 @@
         <v>0.002059</v>
       </c>
       <c r="Y242" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z242" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA242" s="3" t="n">
         <v>0</v>
@@ -28688,7 +28688,7 @@
         <v>0.001248</v>
       </c>
       <c r="Y246" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z246" s="3" t="n">
         <v>0</v>
@@ -28888,10 +28888,10 @@
         <v>0.001999</v>
       </c>
       <c r="Y248" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z248" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA248" s="3" t="n">
         <v>0</v>
@@ -29088,7 +29088,7 @@
         <v>0.001577</v>
       </c>
       <c r="Y250" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z250" s="3" t="n">
         <v>-0</v>
@@ -29188,10 +29188,10 @@
         <v>0.001556</v>
       </c>
       <c r="Y251" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z251" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA251" s="3" t="n">
         <v>0</v>
@@ -29288,7 +29288,7 @@
         <v>0.001036</v>
       </c>
       <c r="Y252" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z252" s="3" t="n">
         <v>0</v>
@@ -29388,7 +29388,7 @@
         <v>0.001663</v>
       </c>
       <c r="Y253" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z253" s="3" t="n">
         <v>-0</v>
@@ -29688,7 +29688,7 @@
         <v>0.001513</v>
       </c>
       <c r="Y256" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z256" s="3" t="n">
         <v>-0</v>
@@ -29988,10 +29988,10 @@
         <v>0.00209</v>
       </c>
       <c r="Y259" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z259" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA259" s="3" t="n">
         <v>1</v>
@@ -30091,7 +30091,7 @@
         <v>0</v>
       </c>
       <c r="Z260" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA260" s="3" t="n">
         <v>0</v>
@@ -30388,7 +30388,7 @@
         <v>0.000785</v>
       </c>
       <c r="Y263" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z263" s="3" t="n">
         <v>-0</v>
@@ -30488,7 +30488,7 @@
         <v>0.001378</v>
       </c>
       <c r="Y264" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z264" s="3" t="n">
         <v>0</v>
@@ -30991,7 +30991,7 @@
         <v>-0</v>
       </c>
       <c r="Z269" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA269" s="3" t="n">
         <v>1</v>
@@ -31188,7 +31188,7 @@
         <v>0.001877</v>
       </c>
       <c r="Y271" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z271" s="3" t="n">
         <v>0</v>
@@ -31291,7 +31291,7 @@
         <v>0</v>
       </c>
       <c r="Z272" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA272" s="3" t="n">
         <v>0</v>
@@ -31588,7 +31588,7 @@
         <v>0.000804</v>
       </c>
       <c r="Y275" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z275" s="3" t="n">
         <v>-0</v>
@@ -31788,10 +31788,10 @@
         <v>0.001352</v>
       </c>
       <c r="Y277" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z277" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA277" s="3" t="n">
         <v>0</v>
@@ -32188,10 +32188,10 @@
         <v>0.00087</v>
       </c>
       <c r="Y281" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z281" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA281" s="3" t="n">
         <v>1</v>
@@ -32288,7 +32288,7 @@
         <v>0.00126</v>
       </c>
       <c r="Y282" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z282" s="3" t="n">
         <v>0</v>
@@ -32391,7 +32391,7 @@
         <v>0</v>
       </c>
       <c r="Z283" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA283" s="3" t="n">
         <v>0</v>
@@ -32491,7 +32491,7 @@
         <v>0</v>
       </c>
       <c r="Z284" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA284" s="3" t="n">
         <v>0</v>
@@ -32788,7 +32788,7 @@
         <v>0.00315</v>
       </c>
       <c r="Y287" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z287" s="3" t="n">
         <v>-0</v>
@@ -33088,10 +33088,10 @@
         <v>0.001506</v>
       </c>
       <c r="Y290" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z290" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA290" s="3" t="n">
         <v>2</v>
@@ -33491,7 +33491,7 @@
         <v>0</v>
       </c>
       <c r="Z294" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA294" s="3" t="n">
         <v>1</v>
@@ -33588,7 +33588,7 @@
         <v>0.001087</v>
       </c>
       <c r="Y295" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z295" s="3" t="n">
         <v>-0</v>
@@ -33788,10 +33788,10 @@
         <v>0.001133</v>
       </c>
       <c r="Y297" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z297" s="3" t="n">
         <v>-0</v>
-      </c>
-      <c r="Z297" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="AA297" s="3" t="n">
         <v>0</v>
@@ -33888,7 +33888,7 @@
         <v>0.00108</v>
       </c>
       <c r="Y298" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z298" s="3" t="n">
         <v>0</v>
@@ -34088,10 +34088,10 @@
         <v>0.000803</v>
       </c>
       <c r="Y300" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z300" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA300" s="3" t="n">
         <v>0</v>
@@ -34391,7 +34391,7 @@
         <v>0</v>
       </c>
       <c r="Z303" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA303" s="3" t="n">
         <v>0</v>
@@ -34488,10 +34488,10 @@
         <v>0.001097</v>
       </c>
       <c r="Y304" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z304" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA304" s="3" t="n">
         <v>0</v>
@@ -34588,7 +34588,7 @@
         <v>0.000908</v>
       </c>
       <c r="Y305" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z305" s="3" t="n">
         <v>-0</v>
@@ -34888,10 +34888,10 @@
         <v>0.000773</v>
       </c>
       <c r="Y308" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z308" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA308" s="3" t="n">
         <v>0</v>
@@ -35188,7 +35188,7 @@
         <v>0.000919</v>
       </c>
       <c r="Y311" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z311" s="3" t="n">
         <v>0</v>
@@ -35291,7 +35291,7 @@
         <v>0</v>
       </c>
       <c r="Z312" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA312" s="3" t="n">
         <v>1</v>
@@ -35388,10 +35388,10 @@
         <v>0.001184</v>
       </c>
       <c r="Y313" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z313" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA313" s="3" t="n">
         <v>0</v>
@@ -35691,7 +35691,7 @@
         <v>0</v>
       </c>
       <c r="Z316" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA316" s="3" t="n">
         <v>0</v>
@@ -36088,10 +36088,10 @@
         <v>0.001123</v>
       </c>
       <c r="Y320" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z320" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA320" s="3" t="n">
         <v>0</v>
@@ -36188,7 +36188,7 @@
         <v>0.001202</v>
       </c>
       <c r="Y321" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z321" s="3" t="n">
         <v>-0</v>
@@ -36388,10 +36388,10 @@
         <v>0.000819</v>
       </c>
       <c r="Y323" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z323" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA323" s="3" t="n">
         <v>3</v>
@@ -37188,10 +37188,10 @@
         <v>0.000763</v>
       </c>
       <c r="Y331" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z331" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA331" s="3" t="n">
         <v>0</v>
@@ -37788,10 +37788,10 @@
         <v>0.00122</v>
       </c>
       <c r="Y337" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z337" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA337" s="3" t="n">
         <v>0</v>
@@ -37988,7 +37988,7 @@
         <v>0.001202</v>
       </c>
       <c r="Y339" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z339" s="3" t="n">
         <v>-0</v>
@@ -38191,7 +38191,7 @@
         <v>0</v>
       </c>
       <c r="Z341" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA341" s="3" t="n">
         <v>0</v>
@@ -38388,10 +38388,10 @@
         <v>0.000725</v>
       </c>
       <c r="Y343" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z343" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA343" s="3" t="n">
         <v>1</v>
@@ -38488,10 +38488,10 @@
         <v>0.000561</v>
       </c>
       <c r="Y344" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z344" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA344" s="3" t="n">
         <v>0</v>
@@ -38791,7 +38791,7 @@
         <v>0</v>
       </c>
       <c r="Z347" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA347" s="3" t="n">
         <v>0</v>
@@ -39564,10 +39564,10 @@
         <v>0.529801</v>
       </c>
       <c r="Y356" s="3" t="n">
-        <v>0.187555</v>
+        <v>0.056172</v>
       </c>
       <c r="Z356" s="3" t="n">
-        <v>0.153199</v>
+        <v>0.097237</v>
       </c>
       <c r="AB356" s="3" t="n">
         <v>0.636396</v>
@@ -39626,10 +39626,10 @@
         <v>0.445424</v>
       </c>
       <c r="Y358" s="3" t="n">
-        <v>0.389592</v>
+        <v>0.333897</v>
       </c>
       <c r="Z358" s="3" t="n">
-        <v>0.383278</v>
+        <v>0.359999</v>
       </c>
       <c r="AA358" s="3" t="n">
         <v>0.552936</v>
@@ -40001,10 +40001,10 @@
         <v>0.386474</v>
       </c>
       <c r="D8" t="n">
-        <v>0.389592</v>
+        <v>0.333897</v>
       </c>
       <c r="E8" t="n">
-        <v>0.299688</v>
+        <v>0.24994</v>
       </c>
       <c r="F8" t="n">
         <v>0.2988505747126437</v>
@@ -40031,10 +40031,10 @@
         <v>0.216528</v>
       </c>
       <c r="D9" t="n">
-        <v>0.187555</v>
+        <v>0.056172</v>
       </c>
       <c r="E9" t="n">
-        <v>0.145364</v>
+        <v>0.039704</v>
       </c>
       <c r="F9" t="n">
         <v>0.1641791044776119</v>
@@ -40061,10 +40061,10 @@
         <v>0.41859</v>
       </c>
       <c r="D10" t="n">
-        <v>0.341349</v>
+        <v>0.308625</v>
       </c>
       <c r="E10" t="n">
-        <v>0.276333</v>
+        <v>0.250795</v>
       </c>
       <c r="F10" t="n">
         <v>0.3636363636363636</v>
@@ -40091,10 +40091,10 @@
         <v>0.397421</v>
       </c>
       <c r="D11" t="n">
-        <v>0.383278</v>
+        <v>0.359999</v>
       </c>
       <c r="E11" t="n">
-        <v>0.291319</v>
+        <v>0.265068</v>
       </c>
       <c r="F11" t="n">
         <v>0.3333333333333333</v>
@@ -40121,10 +40121,10 @@
         <v>0.219019</v>
       </c>
       <c r="D12" t="n">
-        <v>0.153199</v>
+        <v>0.097237</v>
       </c>
       <c r="E12" t="n">
-        <v>0.115539</v>
+        <v>0.07306799999999999</v>
       </c>
       <c r="F12" t="n">
         <v>0.1716417910447761</v>
@@ -40151,10 +40151,10 @@
         <v>0.43754</v>
       </c>
       <c r="D13" t="n">
-        <v>0.339125</v>
+        <v>0.338782</v>
       </c>
       <c r="E13" t="n">
-        <v>0.274709</v>
+        <v>0.276893</v>
       </c>
       <c r="F13" t="n">
         <v>0.3939393939393939</v>

--- a/EpiRank_改/ERA_result_seqday_d_0.95_loops_305.xlsx
+++ b/EpiRank_改/ERA_result_seqday_d_0.95_loops_305.xlsx
@@ -1024,10 +1024,10 @@
         <v>0.01205</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA4" s="3" t="n">
         <v>11</v>
@@ -1938,10 +1938,10 @@
         <v>0.011997</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA10" s="3" t="n">
         <v>4</v>
@@ -2248,10 +2248,10 @@
         <v>0.006602</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA12" s="3" t="n">
         <v>6</v>
@@ -2403,10 +2403,10 @@
         <v>0.004698</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA13" s="3" t="n">
         <v>4</v>
@@ -3708,7 +3708,7 @@
         <v>0.004713</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z22" s="3" t="n">
         <v>0</v>
@@ -4228,10 +4228,10 @@
         <v>0.005408</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA26" s="3" t="n">
         <v>7</v>
@@ -4491,7 +4491,7 @@
         <v>-0</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA28" s="3" t="n">
         <v>8</v>
@@ -4988,10 +4988,10 @@
         <v>0.009729</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA32" s="3" t="n">
         <v>24</v>
@@ -6188,10 +6188,10 @@
         <v>0.01038</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z42" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA42" s="3" t="n">
         <v>0</v>
@@ -7031,7 +7031,7 @@
         <v>-0</v>
       </c>
       <c r="Z49" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA49" s="3" t="n">
         <v>5</v>
@@ -7148,10 +7148,10 @@
         <v>0.004587</v>
       </c>
       <c r="Y50" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z50" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA50" s="3" t="n">
         <v>2</v>
@@ -7988,7 +7988,7 @@
         <v>0.005555</v>
       </c>
       <c r="Y57" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z57" s="3" t="n">
         <v>0</v>
@@ -8588,10 +8588,10 @@
         <v>0.002648</v>
       </c>
       <c r="Y62" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z62" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA62" s="3" t="n">
         <v>4</v>
@@ -9548,7 +9548,7 @@
         <v>0.004618</v>
       </c>
       <c r="Y70" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z70" s="3" t="n">
         <v>0</v>
@@ -9988,7 +9988,7 @@
         <v>0.002616</v>
       </c>
       <c r="Y74" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z74" s="3" t="n">
         <v>0</v>
@@ -11858,10 +11858,10 @@
         <v>0.002613</v>
       </c>
       <c r="Y91" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z91" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA91" s="3" t="n">
         <v>2</v>
@@ -12188,10 +12188,10 @@
         <v>0.002947</v>
       </c>
       <c r="Y94" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z94" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA94" s="3" t="n">
         <v>3</v>
@@ -13071,7 +13071,7 @@
         <v>-0</v>
       </c>
       <c r="Z102" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA102" s="3" t="n">
         <v>0</v>
@@ -13288,10 +13288,10 @@
         <v>0.003369</v>
       </c>
       <c r="Y104" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z104" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA104" s="3" t="n">
         <v>2</v>
@@ -13398,10 +13398,10 @@
         <v>0.003781</v>
       </c>
       <c r="Y105" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z105" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA105" s="3" t="n">
         <v>0</v>
@@ -13618,10 +13618,10 @@
         <v>0.002014</v>
       </c>
       <c r="Y107" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z107" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA107" s="3" t="n">
         <v>3</v>
@@ -14168,10 +14168,10 @@
         <v>0.003672</v>
       </c>
       <c r="Y112" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z112" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA112" s="3" t="n">
         <v>0</v>
@@ -14388,7 +14388,7 @@
         <v>0.002496</v>
       </c>
       <c r="Y114" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z114" s="3" t="n">
         <v>-0</v>
@@ -14611,7 +14611,7 @@
         <v>-0</v>
       </c>
       <c r="Z116" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA116" s="3" t="n">
         <v>1</v>
@@ -14718,10 +14718,10 @@
         <v>0.0059</v>
       </c>
       <c r="Y117" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z117" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA117" s="3" t="n">
         <v>0</v>
@@ -14828,10 +14828,10 @@
         <v>0.002833</v>
       </c>
       <c r="Y118" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z118" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA118" s="3" t="n">
         <v>0</v>
@@ -15048,10 +15048,10 @@
         <v>0.003882</v>
       </c>
       <c r="Y120" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z120" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA120" s="3" t="n">
         <v>0</v>
@@ -15271,7 +15271,7 @@
         <v>0</v>
       </c>
       <c r="Z122" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA122" s="3" t="n">
         <v>2</v>
@@ -15378,7 +15378,7 @@
         <v>0.00191</v>
       </c>
       <c r="Y123" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z123" s="3" t="n">
         <v>0</v>
@@ -15488,10 +15488,10 @@
         <v>0.001759</v>
       </c>
       <c r="Y124" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z124" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA124" s="3" t="n">
         <v>1</v>
@@ -16368,10 +16368,10 @@
         <v>0.002787</v>
       </c>
       <c r="Y132" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z132" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA132" s="3" t="n">
         <v>2</v>
@@ -16478,7 +16478,7 @@
         <v>0.002594</v>
       </c>
       <c r="Y133" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z133" s="3" t="n">
         <v>0</v>
@@ -16588,10 +16588,10 @@
         <v>0.003344</v>
       </c>
       <c r="Y134" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z134" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA134" s="3" t="n">
         <v>3</v>
@@ -16698,10 +16698,10 @@
         <v>0.002116</v>
       </c>
       <c r="Y135" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z135" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA135" s="3" t="n">
         <v>0</v>
@@ -16918,10 +16918,10 @@
         <v>0.002381</v>
       </c>
       <c r="Y137" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z137" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA137" s="3" t="n">
         <v>2</v>
@@ -17031,7 +17031,7 @@
         <v>0</v>
       </c>
       <c r="Z138" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA138" s="3" t="n">
         <v>0</v>
@@ -18128,10 +18128,10 @@
         <v>0.002964</v>
       </c>
       <c r="Y148" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z148" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA148" s="3" t="n">
         <v>3</v>
@@ -18458,10 +18458,10 @@
         <v>0.003403</v>
       </c>
       <c r="Y151" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z151" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA151" s="3" t="n">
         <v>0</v>
@@ -19011,7 +19011,7 @@
         <v>0</v>
       </c>
       <c r="Z156" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA156" s="3" t="n">
         <v>0</v>
@@ -19231,7 +19231,7 @@
         <v>0</v>
       </c>
       <c r="Z158" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA158" s="3" t="n">
         <v>1</v>
@@ -19341,7 +19341,7 @@
         <v>-0</v>
       </c>
       <c r="Z159" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA159" s="3" t="n">
         <v>1</v>
@@ -19888,10 +19888,10 @@
         <v>0.001307</v>
       </c>
       <c r="Y164" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z164" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA164" s="3" t="n">
         <v>0</v>
@@ -20218,10 +20218,10 @@
         <v>0.001621</v>
       </c>
       <c r="Y167" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z167" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA167" s="3" t="n">
         <v>2</v>
@@ -20658,10 +20658,10 @@
         <v>0.002432</v>
       </c>
       <c r="Y171" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z171" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA171" s="3" t="n">
         <v>1</v>
@@ -20768,7 +20768,7 @@
         <v>0.001501</v>
       </c>
       <c r="Y172" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z172" s="3" t="n">
         <v>0</v>
@@ -20878,7 +20878,7 @@
         <v>0.004587</v>
       </c>
       <c r="Y173" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z173" s="3" t="n">
         <v>0</v>
@@ -20988,10 +20988,10 @@
         <v>0.002004</v>
       </c>
       <c r="Y174" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z174" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA174" s="3" t="n">
         <v>2</v>
@@ -21098,10 +21098,10 @@
         <v>0.001399</v>
       </c>
       <c r="Y175" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z175" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA175" s="3" t="n">
         <v>1</v>
@@ -21208,10 +21208,10 @@
         <v>0.003002</v>
       </c>
       <c r="Y176" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z176" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA176" s="3" t="n">
         <v>0</v>
@@ -21321,7 +21321,7 @@
         <v>0</v>
       </c>
       <c r="Z177" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA177" s="3" t="n">
         <v>2</v>
@@ -22088,7 +22088,7 @@
         <v>0.005244</v>
       </c>
       <c r="Y184" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z184" s="3" t="n">
         <v>-0</v>
@@ -22308,10 +22308,10 @@
         <v>0.001326</v>
       </c>
       <c r="Y186" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z186" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA186" s="3" t="n">
         <v>0</v>
@@ -22748,10 +22748,10 @@
         <v>0.002542</v>
       </c>
       <c r="Y190" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z190" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA190" s="3" t="n">
         <v>1</v>
@@ -22858,7 +22858,7 @@
         <v>0.002618</v>
       </c>
       <c r="Y191" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z191" s="3" t="n">
         <v>0</v>
@@ -22968,10 +22968,10 @@
         <v>0.001259</v>
       </c>
       <c r="Y192" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z192" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA192" s="3" t="n">
         <v>1</v>
@@ -23081,7 +23081,7 @@
         <v>0</v>
       </c>
       <c r="Z193" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA193" s="3" t="n">
         <v>1</v>
@@ -23518,10 +23518,10 @@
         <v>0.002087</v>
       </c>
       <c r="Y197" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z197" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA197" s="3" t="n">
         <v>0</v>
@@ -24178,7 +24178,7 @@
         <v>0.001669</v>
       </c>
       <c r="Y203" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z203" s="3" t="n">
         <v>-0</v>
@@ -24288,10 +24288,10 @@
         <v>0.001495</v>
       </c>
       <c r="Y204" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z204" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA204" s="3" t="n">
         <v>6</v>
@@ -24728,10 +24728,10 @@
         <v>0.001245</v>
       </c>
       <c r="Y208" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z208" s="3" t="n">
         <v>-0</v>
-      </c>
-      <c r="Z208" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="AA208" s="3" t="n">
         <v>0</v>
@@ -24951,7 +24951,7 @@
         <v>0</v>
       </c>
       <c r="Z210" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA210" s="3" t="n">
         <v>1</v>
@@ -25058,10 +25058,10 @@
         <v>0.0008140000000000001</v>
       </c>
       <c r="Y211" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z211" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA211" s="3" t="n">
         <v>0</v>
@@ -25168,7 +25168,7 @@
         <v>0.001943</v>
       </c>
       <c r="Y212" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z212" s="3" t="n">
         <v>0</v>
@@ -25718,7 +25718,7 @@
         <v>0.001237</v>
       </c>
       <c r="Y217" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z217" s="3" t="n">
         <v>0</v>
@@ -25828,10 +25828,10 @@
         <v>0.002238</v>
       </c>
       <c r="Y218" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z218" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA218" s="3" t="n">
         <v>0</v>
@@ -26268,7 +26268,7 @@
         <v>0.001</v>
       </c>
       <c r="Y222" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z222" s="3" t="n">
         <v>0</v>
@@ -26688,10 +26688,10 @@
         <v>0.00125</v>
       </c>
       <c r="Y226" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z226" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA226" s="3" t="n">
         <v>0</v>
@@ -26791,7 +26791,7 @@
         <v>-0</v>
       </c>
       <c r="Z227" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA227" s="3" t="n">
         <v>0</v>
@@ -27091,7 +27091,7 @@
         <v>-0</v>
       </c>
       <c r="Z230" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA230" s="3" t="n">
         <v>0</v>
@@ -27191,7 +27191,7 @@
         <v>0</v>
       </c>
       <c r="Z231" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA231" s="3" t="n">
         <v>0</v>
@@ -27288,10 +27288,10 @@
         <v>0.00185</v>
       </c>
       <c r="Y232" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z232" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA232" s="3" t="n">
         <v>2</v>
@@ -27391,7 +27391,7 @@
         <v>-0</v>
       </c>
       <c r="Z233" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA233" s="3" t="n">
         <v>0</v>
@@ -27891,7 +27891,7 @@
         <v>-0</v>
       </c>
       <c r="Z238" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA238" s="3" t="n">
         <v>0</v>
@@ -27988,7 +27988,7 @@
         <v>0.00079</v>
       </c>
       <c r="Y239" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z239" s="3" t="n">
         <v>0</v>
@@ -28091,7 +28091,7 @@
         <v>0</v>
       </c>
       <c r="Z240" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA240" s="3" t="n">
         <v>0</v>
@@ -28691,7 +28691,7 @@
         <v>-0</v>
       </c>
       <c r="Z246" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA246" s="3" t="n">
         <v>0</v>
@@ -28991,7 +28991,7 @@
         <v>-0</v>
       </c>
       <c r="Z249" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA249" s="3" t="n">
         <v>0</v>
@@ -29088,7 +29088,7 @@
         <v>0.001577</v>
       </c>
       <c r="Y250" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z250" s="3" t="n">
         <v>-0</v>
@@ -29188,10 +29188,10 @@
         <v>0.001556</v>
       </c>
       <c r="Y251" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z251" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA251" s="3" t="n">
         <v>0</v>
@@ -29291,7 +29291,7 @@
         <v>-0</v>
       </c>
       <c r="Z252" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA252" s="3" t="n">
         <v>2</v>
@@ -29388,10 +29388,10 @@
         <v>0.001663</v>
       </c>
       <c r="Y253" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z253" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA253" s="3" t="n">
         <v>0</v>
@@ -29991,7 +29991,7 @@
         <v>-0</v>
       </c>
       <c r="Z259" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA259" s="3" t="n">
         <v>1</v>
@@ -30088,10 +30088,10 @@
         <v>0.00143</v>
       </c>
       <c r="Y260" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z260" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA260" s="3" t="n">
         <v>0</v>
@@ -30288,10 +30288,10 @@
         <v>0.001019</v>
       </c>
       <c r="Y262" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z262" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA262" s="3" t="n">
         <v>0</v>
@@ -30388,10 +30388,10 @@
         <v>0.000785</v>
       </c>
       <c r="Y263" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z263" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA263" s="3" t="n">
         <v>0</v>
@@ -30491,7 +30491,7 @@
         <v>-0</v>
       </c>
       <c r="Z264" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA264" s="3" t="n">
         <v>2</v>
@@ -30791,7 +30791,7 @@
         <v>0</v>
       </c>
       <c r="Z267" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA267" s="3" t="n">
         <v>0</v>
@@ -30891,7 +30891,7 @@
         <v>0</v>
       </c>
       <c r="Z268" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA268" s="3" t="n">
         <v>0</v>
@@ -30991,7 +30991,7 @@
         <v>-0</v>
       </c>
       <c r="Z269" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA269" s="3" t="n">
         <v>1</v>
@@ -31188,7 +31188,7 @@
         <v>0.001877</v>
       </c>
       <c r="Y271" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z271" s="3" t="n">
         <v>0</v>
@@ -31288,10 +31288,10 @@
         <v>0.001118</v>
       </c>
       <c r="Y272" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z272" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA272" s="3" t="n">
         <v>0</v>
@@ -32291,7 +32291,7 @@
         <v>-0</v>
       </c>
       <c r="Z282" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA282" s="3" t="n">
         <v>0</v>
@@ -32488,7 +32488,7 @@
         <v>0.0009479999999999999</v>
       </c>
       <c r="Y284" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z284" s="3" t="n">
         <v>-0</v>
@@ -33088,10 +33088,10 @@
         <v>0.001506</v>
       </c>
       <c r="Y290" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z290" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA290" s="3" t="n">
         <v>2</v>
@@ -33491,7 +33491,7 @@
         <v>0</v>
       </c>
       <c r="Z294" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA294" s="3" t="n">
         <v>1</v>
@@ -33588,10 +33588,10 @@
         <v>0.001087</v>
       </c>
       <c r="Y295" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z295" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA295" s="3" t="n">
         <v>9</v>
@@ -34091,7 +34091,7 @@
         <v>-0</v>
       </c>
       <c r="Z300" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA300" s="3" t="n">
         <v>0</v>
@@ -34391,7 +34391,7 @@
         <v>0</v>
       </c>
       <c r="Z303" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA303" s="3" t="n">
         <v>0</v>
@@ -34488,7 +34488,7 @@
         <v>0.001097</v>
       </c>
       <c r="Y304" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z304" s="3" t="n">
         <v>0</v>
@@ -34588,10 +34588,10 @@
         <v>0.000908</v>
       </c>
       <c r="Y305" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z305" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA305" s="3" t="n">
         <v>0</v>
@@ -35291,7 +35291,7 @@
         <v>0</v>
       </c>
       <c r="Z312" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA312" s="3" t="n">
         <v>1</v>
@@ -35791,7 +35791,7 @@
         <v>0</v>
       </c>
       <c r="Z317" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA317" s="3" t="n">
         <v>1</v>
@@ -36188,7 +36188,7 @@
         <v>0.001202</v>
       </c>
       <c r="Y321" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z321" s="3" t="n">
         <v>-0</v>
@@ -36391,7 +36391,7 @@
         <v>-0</v>
       </c>
       <c r="Z323" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA323" s="3" t="n">
         <v>3</v>
@@ -37791,7 +37791,7 @@
         <v>-0</v>
       </c>
       <c r="Z337" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA337" s="3" t="n">
         <v>0</v>
@@ -38188,7 +38188,7 @@
         <v>0.001203</v>
       </c>
       <c r="Y341" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z341" s="3" t="n">
         <v>0</v>
@@ -38391,7 +38391,7 @@
         <v>-0</v>
       </c>
       <c r="Z343" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA343" s="3" t="n">
         <v>1</v>
@@ -38491,7 +38491,7 @@
         <v>-0</v>
       </c>
       <c r="Z344" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA344" s="3" t="n">
         <v>0</v>
@@ -38788,10 +38788,10 @@
         <v>0.000592</v>
       </c>
       <c r="Y347" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z347" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA347" s="3" t="n">
         <v>0</v>
@@ -39288,10 +39288,10 @@
         <v>0.000518</v>
       </c>
       <c r="Y352" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z352" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA352" s="3" t="n">
         <v>0</v>
@@ -39564,10 +39564,10 @@
         <v>0.529801</v>
       </c>
       <c r="Y356" s="3" t="n">
-        <v>0.056172</v>
+        <v>0.06324</v>
       </c>
       <c r="Z356" s="3" t="n">
-        <v>0.097237</v>
+        <v>0.065718</v>
       </c>
       <c r="AB356" s="3" t="n">
         <v>0.636396</v>
@@ -39626,10 +39626,10 @@
         <v>0.445424</v>
       </c>
       <c r="Y358" s="3" t="n">
-        <v>0.333897</v>
+        <v>0.319182</v>
       </c>
       <c r="Z358" s="3" t="n">
-        <v>0.359999</v>
+        <v>0.344026</v>
       </c>
       <c r="AA358" s="3" t="n">
         <v>0.552936</v>
@@ -40001,10 +40001,10 @@
         <v>0.386474</v>
       </c>
       <c r="D8" t="n">
-        <v>0.333897</v>
+        <v>0.319182</v>
       </c>
       <c r="E8" t="n">
-        <v>0.24994</v>
+        <v>0.244253</v>
       </c>
       <c r="F8" t="n">
         <v>0.2988505747126437</v>
@@ -40031,10 +40031,10 @@
         <v>0.216528</v>
       </c>
       <c r="D9" t="n">
-        <v>0.056172</v>
+        <v>0.06324</v>
       </c>
       <c r="E9" t="n">
-        <v>0.039704</v>
+        <v>0.05039</v>
       </c>
       <c r="F9" t="n">
         <v>0.1641791044776119</v>
@@ -40061,10 +40061,10 @@
         <v>0.41859</v>
       </c>
       <c r="D10" t="n">
-        <v>0.308625</v>
+        <v>0.273495</v>
       </c>
       <c r="E10" t="n">
-        <v>0.250795</v>
+        <v>0.220047</v>
       </c>
       <c r="F10" t="n">
         <v>0.3636363636363636</v>
@@ -40091,10 +40091,10 @@
         <v>0.397421</v>
       </c>
       <c r="D11" t="n">
-        <v>0.359999</v>
+        <v>0.344026</v>
       </c>
       <c r="E11" t="n">
-        <v>0.265068</v>
+        <v>0.258237</v>
       </c>
       <c r="F11" t="n">
         <v>0.3333333333333333</v>
@@ -40121,10 +40121,10 @@
         <v>0.219019</v>
       </c>
       <c r="D12" t="n">
-        <v>0.097237</v>
+        <v>0.065718</v>
       </c>
       <c r="E12" t="n">
-        <v>0.07306799999999999</v>
+        <v>0.052143</v>
       </c>
       <c r="F12" t="n">
         <v>0.1716417910447761</v>
@@ -40151,10 +40151,10 @@
         <v>0.43754</v>
       </c>
       <c r="D13" t="n">
-        <v>0.338782</v>
+        <v>0.275899</v>
       </c>
       <c r="E13" t="n">
-        <v>0.276893</v>
+        <v>0.222624</v>
       </c>
       <c r="F13" t="n">
         <v>0.3939393939393939</v>

--- a/EpiRank_改/ERA_result_seqday_d_0.95_loops_305.xlsx
+++ b/EpiRank_改/ERA_result_seqday_d_0.95_loops_305.xlsx
@@ -714,10 +714,10 @@
         <v>0.012835</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA2" s="3" t="n">
         <v>9</v>
@@ -869,10 +869,10 @@
         <v>0.006652</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA3" s="3" t="n">
         <v>11</v>
@@ -1024,10 +1024,10 @@
         <v>0.01205</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA4" s="3" t="n">
         <v>11</v>
@@ -1179,10 +1179,10 @@
         <v>0.012838</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA5" s="3" t="n">
         <v>11</v>
@@ -1485,10 +1485,10 @@
         <v>0.009434</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA7" s="3" t="n">
         <v>2</v>
@@ -2248,10 +2248,10 @@
         <v>0.006602</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA12" s="3" t="n">
         <v>6</v>
@@ -2403,10 +2403,10 @@
         <v>0.004698</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA13" s="3" t="n">
         <v>4</v>
@@ -3008,10 +3008,10 @@
         <v>0.008274999999999999</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA17" s="3" t="n">
         <v>4</v>
@@ -3148,10 +3148,10 @@
         <v>0.008586</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA18" s="3" t="n">
         <v>3</v>
@@ -4488,7 +4488,7 @@
         <v>0.007023</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z28" s="3" t="n">
         <v>-0</v>
@@ -5348,10 +5348,10 @@
         <v>0.008265</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA35" s="3" t="n">
         <v>5</v>
@@ -5828,10 +5828,10 @@
         <v>0.004917</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA39" s="3" t="n">
         <v>2</v>
@@ -6788,10 +6788,10 @@
         <v>0.007706</v>
       </c>
       <c r="Y47" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z47" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA47" s="3" t="n">
         <v>2</v>
@@ -7028,10 +7028,10 @@
         <v>0.006149</v>
       </c>
       <c r="Y49" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z49" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA49" s="3" t="n">
         <v>5</v>
@@ -7148,10 +7148,10 @@
         <v>0.004587</v>
       </c>
       <c r="Y50" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z50" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA50" s="3" t="n">
         <v>2</v>
@@ -7751,7 +7751,7 @@
         <v>0</v>
       </c>
       <c r="Z55" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA55" s="3" t="n">
         <v>1</v>
@@ -8591,7 +8591,7 @@
         <v>0</v>
       </c>
       <c r="Z62" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA62" s="3" t="n">
         <v>4</v>
@@ -9551,7 +9551,7 @@
         <v>-0</v>
       </c>
       <c r="Z70" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA70" s="3" t="n">
         <v>6</v>
@@ -9991,7 +9991,7 @@
         <v>-0</v>
       </c>
       <c r="Z74" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA74" s="3" t="n">
         <v>2</v>
@@ -10098,10 +10098,10 @@
         <v>0.006096</v>
       </c>
       <c r="Y75" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z75" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA75" s="3" t="n">
         <v>1</v>
@@ -10651,7 +10651,7 @@
         <v>0</v>
       </c>
       <c r="Z80" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA80" s="3" t="n">
         <v>4</v>
@@ -12078,7 +12078,7 @@
         <v>0.001988</v>
       </c>
       <c r="Y93" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z93" s="3" t="n">
         <v>0</v>
@@ -12188,7 +12188,7 @@
         <v>0.002947</v>
       </c>
       <c r="Y94" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z94" s="3" t="n">
         <v>-0</v>
@@ -12628,10 +12628,10 @@
         <v>0.003197</v>
       </c>
       <c r="Y98" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z98" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA98" s="3" t="n">
         <v>1</v>
@@ -13068,7 +13068,7 @@
         <v>0.002268</v>
       </c>
       <c r="Y102" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z102" s="3" t="n">
         <v>0</v>
@@ -13288,10 +13288,10 @@
         <v>0.003369</v>
       </c>
       <c r="Y104" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z104" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA104" s="3" t="n">
         <v>2</v>
@@ -13398,10 +13398,10 @@
         <v>0.003781</v>
       </c>
       <c r="Y105" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z105" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA105" s="3" t="n">
         <v>0</v>
@@ -13618,10 +13618,10 @@
         <v>0.002014</v>
       </c>
       <c r="Y107" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z107" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA107" s="3" t="n">
         <v>3</v>
@@ -14388,10 +14388,10 @@
         <v>0.002496</v>
       </c>
       <c r="Y114" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z114" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA114" s="3" t="n">
         <v>1</v>
@@ -14611,7 +14611,7 @@
         <v>-0</v>
       </c>
       <c r="Z116" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA116" s="3" t="n">
         <v>1</v>
@@ -14938,10 +14938,10 @@
         <v>0.002833</v>
       </c>
       <c r="Y119" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z119" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA119" s="3" t="n">
         <v>1</v>
@@ -15158,10 +15158,10 @@
         <v>0.001286</v>
       </c>
       <c r="Y121" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z121" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA121" s="3" t="n">
         <v>1</v>
@@ -15378,10 +15378,10 @@
         <v>0.00191</v>
       </c>
       <c r="Y123" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z123" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA123" s="3" t="n">
         <v>1</v>
@@ -15488,10 +15488,10 @@
         <v>0.001759</v>
       </c>
       <c r="Y124" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z124" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA124" s="3" t="n">
         <v>1</v>
@@ -16368,10 +16368,10 @@
         <v>0.002787</v>
       </c>
       <c r="Y132" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z132" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA132" s="3" t="n">
         <v>2</v>
@@ -16588,10 +16588,10 @@
         <v>0.003344</v>
       </c>
       <c r="Y134" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z134" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA134" s="3" t="n">
         <v>3</v>
@@ -16808,10 +16808,10 @@
         <v>0.002579</v>
       </c>
       <c r="Y136" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z136" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA136" s="3" t="n">
         <v>0</v>
@@ -16918,10 +16918,10 @@
         <v>0.002381</v>
       </c>
       <c r="Y137" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z137" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA137" s="3" t="n">
         <v>2</v>
@@ -17031,7 +17031,7 @@
         <v>0</v>
       </c>
       <c r="Z138" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA138" s="3" t="n">
         <v>0</v>
@@ -17358,7 +17358,7 @@
         <v>0.002448</v>
       </c>
       <c r="Y141" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z141" s="3" t="n">
         <v>0</v>
@@ -17688,10 +17688,10 @@
         <v>0.001664</v>
       </c>
       <c r="Y144" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z144" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA144" s="3" t="n">
         <v>0</v>
@@ -17801,7 +17801,7 @@
         <v>0</v>
       </c>
       <c r="Z145" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA145" s="3" t="n">
         <v>0</v>
@@ -18128,10 +18128,10 @@
         <v>0.002964</v>
       </c>
       <c r="Y148" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z148" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA148" s="3" t="n">
         <v>3</v>
@@ -18678,10 +18678,10 @@
         <v>0.001714</v>
       </c>
       <c r="Y153" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z153" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA153" s="3" t="n">
         <v>2</v>
@@ -18898,10 +18898,10 @@
         <v>0.001295</v>
       </c>
       <c r="Y155" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z155" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA155" s="3" t="n">
         <v>0</v>
@@ -19011,7 +19011,7 @@
         <v>0</v>
       </c>
       <c r="Z156" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA156" s="3" t="n">
         <v>0</v>
@@ -19231,7 +19231,7 @@
         <v>0</v>
       </c>
       <c r="Z158" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA158" s="3" t="n">
         <v>1</v>
@@ -19341,7 +19341,7 @@
         <v>-0</v>
       </c>
       <c r="Z159" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA159" s="3" t="n">
         <v>1</v>
@@ -19671,7 +19671,7 @@
         <v>0</v>
       </c>
       <c r="Z162" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA162" s="3" t="n">
         <v>1</v>
@@ -19891,7 +19891,7 @@
         <v>0</v>
       </c>
       <c r="Z164" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA164" s="3" t="n">
         <v>0</v>
@@ -19998,10 +19998,10 @@
         <v>0.001901</v>
       </c>
       <c r="Y165" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z165" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA165" s="3" t="n">
         <v>0</v>
@@ -20328,10 +20328,10 @@
         <v>0.004473</v>
       </c>
       <c r="Y168" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z168" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA168" s="3" t="n">
         <v>1</v>
@@ -20548,7 +20548,7 @@
         <v>0.00302</v>
       </c>
       <c r="Y170" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z170" s="3" t="n">
         <v>0</v>
@@ -20658,10 +20658,10 @@
         <v>0.002432</v>
       </c>
       <c r="Y171" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z171" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA171" s="3" t="n">
         <v>1</v>
@@ -20768,10 +20768,10 @@
         <v>0.001501</v>
       </c>
       <c r="Y172" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z172" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA172" s="3" t="n">
         <v>1</v>
@@ -20881,7 +20881,7 @@
         <v>-0</v>
       </c>
       <c r="Z173" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA173" s="3" t="n">
         <v>0</v>
@@ -20988,7 +20988,7 @@
         <v>0.002004</v>
       </c>
       <c r="Y174" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z174" s="3" t="n">
         <v>0</v>
@@ -21208,10 +21208,10 @@
         <v>0.003002</v>
       </c>
       <c r="Y176" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z176" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA176" s="3" t="n">
         <v>0</v>
@@ -21431,7 +21431,7 @@
         <v>0</v>
       </c>
       <c r="Z178" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA178" s="3" t="n">
         <v>0</v>
@@ -21758,7 +21758,7 @@
         <v>0.0009700000000000001</v>
       </c>
       <c r="Y181" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z181" s="3" t="n">
         <v>0</v>
@@ -21868,10 +21868,10 @@
         <v>0.001797</v>
       </c>
       <c r="Y182" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z182" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA182" s="3" t="n">
         <v>0</v>
@@ -22088,10 +22088,10 @@
         <v>0.005244</v>
       </c>
       <c r="Y184" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z184" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA184" s="3" t="n">
         <v>2</v>
@@ -22311,7 +22311,7 @@
         <v>-0</v>
       </c>
       <c r="Z186" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA186" s="3" t="n">
         <v>0</v>
@@ -22531,7 +22531,7 @@
         <v>0</v>
       </c>
       <c r="Z188" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA188" s="3" t="n">
         <v>0</v>
@@ -22748,10 +22748,10 @@
         <v>0.002542</v>
       </c>
       <c r="Y190" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z190" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA190" s="3" t="n">
         <v>1</v>
@@ -22968,10 +22968,10 @@
         <v>0.001259</v>
       </c>
       <c r="Y192" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z192" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA192" s="3" t="n">
         <v>1</v>
@@ -23408,10 +23408,10 @@
         <v>0.002813</v>
       </c>
       <c r="Y196" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z196" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA196" s="3" t="n">
         <v>1</v>
@@ -23518,10 +23518,10 @@
         <v>0.002087</v>
       </c>
       <c r="Y197" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z197" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA197" s="3" t="n">
         <v>0</v>
@@ -23628,7 +23628,7 @@
         <v>0.001081</v>
       </c>
       <c r="Y198" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z198" s="3" t="n">
         <v>-0</v>
@@ -23738,10 +23738,10 @@
         <v>0.001708</v>
       </c>
       <c r="Y199" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z199" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA199" s="3" t="n">
         <v>0</v>
@@ -23848,10 +23848,10 @@
         <v>0.002818</v>
       </c>
       <c r="Y200" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z200" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA200" s="3" t="n">
         <v>0</v>
@@ -23958,10 +23958,10 @@
         <v>0.002161</v>
       </c>
       <c r="Y201" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z201" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA201" s="3" t="n">
         <v>0</v>
@@ -24068,10 +24068,10 @@
         <v>0.003364</v>
       </c>
       <c r="Y202" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z202" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA202" s="3" t="n">
         <v>0</v>
@@ -24178,7 +24178,7 @@
         <v>0.001669</v>
       </c>
       <c r="Y203" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z203" s="3" t="n">
         <v>-0</v>
@@ -24288,10 +24288,10 @@
         <v>0.001495</v>
       </c>
       <c r="Y204" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z204" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA204" s="3" t="n">
         <v>6</v>
@@ -24731,7 +24731,7 @@
         <v>0</v>
       </c>
       <c r="Z208" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA208" s="3" t="n">
         <v>0</v>
@@ -25171,7 +25171,7 @@
         <v>0</v>
       </c>
       <c r="Z212" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA212" s="3" t="n">
         <v>0</v>
@@ -25608,10 +25608,10 @@
         <v>0.001782</v>
       </c>
       <c r="Y216" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z216" s="3" t="n">
         <v>-0</v>
-      </c>
-      <c r="Z216" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="AA216" s="3" t="n">
         <v>2</v>
@@ -25721,7 +25721,7 @@
         <v>-0</v>
       </c>
       <c r="Z217" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA217" s="3" t="n">
         <v>5</v>
@@ -25828,10 +25828,10 @@
         <v>0.002238</v>
       </c>
       <c r="Y218" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z218" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA218" s="3" t="n">
         <v>0</v>
@@ -25938,10 +25938,10 @@
         <v>0.001152</v>
       </c>
       <c r="Y219" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z219" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA219" s="3" t="n">
         <v>0</v>
@@ -26161,7 +26161,7 @@
         <v>0</v>
       </c>
       <c r="Z221" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA221" s="3" t="n">
         <v>2</v>
@@ -26271,7 +26271,7 @@
         <v>0</v>
       </c>
       <c r="Z222" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA222" s="3" t="n">
         <v>1</v>
@@ -26381,7 +26381,7 @@
         <v>0</v>
       </c>
       <c r="Z223" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA223" s="3" t="n">
         <v>2</v>
@@ -26488,10 +26488,10 @@
         <v>0.002084</v>
       </c>
       <c r="Y224" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z224" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA224" s="3" t="n">
         <v>2</v>
@@ -26788,7 +26788,7 @@
         <v>0.000905</v>
       </c>
       <c r="Y227" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z227" s="3" t="n">
         <v>0</v>
@@ -27088,10 +27088,10 @@
         <v>0.000867</v>
       </c>
       <c r="Y230" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z230" s="3" t="n">
         <v>-0</v>
-      </c>
-      <c r="Z230" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="AA230" s="3" t="n">
         <v>0</v>
@@ -27188,7 +27188,7 @@
         <v>0.00135</v>
       </c>
       <c r="Y231" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z231" s="3" t="n">
         <v>-0</v>
@@ -27288,10 +27288,10 @@
         <v>0.00185</v>
       </c>
       <c r="Y232" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z232" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA232" s="3" t="n">
         <v>2</v>
@@ -27388,7 +27388,7 @@
         <v>0.001386</v>
       </c>
       <c r="Y233" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z233" s="3" t="n">
         <v>0</v>
@@ -27491,7 +27491,7 @@
         <v>0</v>
       </c>
       <c r="Z234" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA234" s="3" t="n">
         <v>1</v>
@@ -27588,10 +27588,10 @@
         <v>0.000995</v>
       </c>
       <c r="Y235" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z235" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA235" s="3" t="n">
         <v>0</v>
@@ -27788,10 +27788,10 @@
         <v>0.000672</v>
       </c>
       <c r="Y237" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z237" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA237" s="3" t="n">
         <v>2</v>
@@ -28091,7 +28091,7 @@
         <v>0</v>
       </c>
       <c r="Z240" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA240" s="3" t="n">
         <v>0</v>
@@ -28288,10 +28288,10 @@
         <v>0.002059</v>
       </c>
       <c r="Y242" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z242" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA242" s="3" t="n">
         <v>0</v>
@@ -28688,7 +28688,7 @@
         <v>0.001248</v>
       </c>
       <c r="Y246" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z246" s="3" t="n">
         <v>-0</v>
@@ -28888,10 +28888,10 @@
         <v>0.001999</v>
       </c>
       <c r="Y248" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z248" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA248" s="3" t="n">
         <v>0</v>
@@ -28991,7 +28991,7 @@
         <v>-0</v>
       </c>
       <c r="Z249" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA249" s="3" t="n">
         <v>0</v>
@@ -29088,10 +29088,10 @@
         <v>0.001577</v>
       </c>
       <c r="Y250" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z250" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA250" s="3" t="n">
         <v>0</v>
@@ -29188,10 +29188,10 @@
         <v>0.001556</v>
       </c>
       <c r="Y251" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z251" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA251" s="3" t="n">
         <v>0</v>
@@ -29288,7 +29288,7 @@
         <v>0.001036</v>
       </c>
       <c r="Y252" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z252" s="3" t="n">
         <v>-0</v>
@@ -29688,10 +29688,10 @@
         <v>0.001513</v>
       </c>
       <c r="Y256" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z256" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA256" s="3" t="n">
         <v>3</v>
@@ -29788,10 +29788,10 @@
         <v>0.00164</v>
       </c>
       <c r="Y257" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z257" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA257" s="3" t="n">
         <v>0</v>
@@ -29988,7 +29988,7 @@
         <v>0.00209</v>
       </c>
       <c r="Y259" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z259" s="3" t="n">
         <v>0</v>
@@ -30388,10 +30388,10 @@
         <v>0.000785</v>
       </c>
       <c r="Y263" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z263" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA263" s="3" t="n">
         <v>0</v>
@@ -30488,10 +30488,10 @@
         <v>0.001378</v>
       </c>
       <c r="Y264" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z264" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA264" s="3" t="n">
         <v>2</v>
@@ -30588,10 +30588,10 @@
         <v>0.001509</v>
       </c>
       <c r="Y265" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z265" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA265" s="3" t="n">
         <v>0</v>
@@ -30791,7 +30791,7 @@
         <v>0</v>
       </c>
       <c r="Z267" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA267" s="3" t="n">
         <v>0</v>
@@ -30891,7 +30891,7 @@
         <v>0</v>
       </c>
       <c r="Z268" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA268" s="3" t="n">
         <v>0</v>
@@ -31188,7 +31188,7 @@
         <v>0.001877</v>
       </c>
       <c r="Y271" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z271" s="3" t="n">
         <v>0</v>
@@ -31588,7 +31588,7 @@
         <v>0.000804</v>
       </c>
       <c r="Y275" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z275" s="3" t="n">
         <v>-0</v>
@@ -31788,7 +31788,7 @@
         <v>0.001352</v>
       </c>
       <c r="Y277" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z277" s="3" t="n">
         <v>-0</v>
@@ -32188,10 +32188,10 @@
         <v>0.00087</v>
       </c>
       <c r="Y281" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z281" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA281" s="3" t="n">
         <v>1</v>
@@ -32288,10 +32288,10 @@
         <v>0.00126</v>
       </c>
       <c r="Y282" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z282" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA282" s="3" t="n">
         <v>0</v>
@@ -32391,7 +32391,7 @@
         <v>0</v>
       </c>
       <c r="Z283" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA283" s="3" t="n">
         <v>0</v>
@@ -32691,7 +32691,7 @@
         <v>0</v>
       </c>
       <c r="Z286" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA286" s="3" t="n">
         <v>1</v>
@@ -32788,10 +32788,10 @@
         <v>0.00315</v>
       </c>
       <c r="Y287" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z287" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA287" s="3" t="n">
         <v>0</v>
@@ -33088,10 +33088,10 @@
         <v>0.001506</v>
       </c>
       <c r="Y290" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z290" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA290" s="3" t="n">
         <v>2</v>
@@ -33388,10 +33388,10 @@
         <v>0.001773</v>
       </c>
       <c r="Y293" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z293" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA293" s="3" t="n">
         <v>1</v>
@@ -33591,7 +33591,7 @@
         <v>-0</v>
       </c>
       <c r="Z295" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA295" s="3" t="n">
         <v>9</v>
@@ -33791,7 +33791,7 @@
         <v>0</v>
       </c>
       <c r="Z297" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA297" s="3" t="n">
         <v>0</v>
@@ -33888,7 +33888,7 @@
         <v>0.00108</v>
       </c>
       <c r="Y298" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z298" s="3" t="n">
         <v>0</v>
@@ -34088,7 +34088,7 @@
         <v>0.000803</v>
       </c>
       <c r="Y300" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z300" s="3" t="n">
         <v>0</v>
@@ -34488,7 +34488,7 @@
         <v>0.001097</v>
       </c>
       <c r="Y304" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z304" s="3" t="n">
         <v>0</v>
@@ -34588,7 +34588,7 @@
         <v>0.000908</v>
       </c>
       <c r="Y305" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z305" s="3" t="n">
         <v>0</v>
@@ -34888,7 +34888,7 @@
         <v>0.000773</v>
       </c>
       <c r="Y308" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z308" s="3" t="n">
         <v>0</v>
@@ -35188,7 +35188,7 @@
         <v>0.000919</v>
       </c>
       <c r="Y311" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z311" s="3" t="n">
         <v>0</v>
@@ -35288,7 +35288,7 @@
         <v>0.000803</v>
       </c>
       <c r="Y312" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z312" s="3" t="n">
         <v>0</v>
@@ -35388,10 +35388,10 @@
         <v>0.001184</v>
       </c>
       <c r="Y313" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z313" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA313" s="3" t="n">
         <v>0</v>
@@ -35791,7 +35791,7 @@
         <v>0</v>
       </c>
       <c r="Z317" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA317" s="3" t="n">
         <v>1</v>
@@ -36188,7 +36188,7 @@
         <v>0.001202</v>
       </c>
       <c r="Y321" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z321" s="3" t="n">
         <v>-0</v>
@@ -36388,10 +36388,10 @@
         <v>0.000819</v>
       </c>
       <c r="Y323" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z323" s="3" t="n">
         <v>-0</v>
-      </c>
-      <c r="Z323" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="AA323" s="3" t="n">
         <v>3</v>
@@ -36588,10 +36588,10 @@
         <v>0.00087</v>
       </c>
       <c r="Y325" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z325" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA325" s="3" t="n">
         <v>0</v>
@@ -37788,7 +37788,7 @@
         <v>0.00122</v>
       </c>
       <c r="Y337" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z337" s="3" t="n">
         <v>0</v>
@@ -37988,10 +37988,10 @@
         <v>0.001202</v>
       </c>
       <c r="Y339" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z339" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA339" s="3" t="n">
         <v>0</v>
@@ -38191,7 +38191,7 @@
         <v>-0</v>
       </c>
       <c r="Z341" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA341" s="3" t="n">
         <v>0</v>
@@ -38391,7 +38391,7 @@
         <v>-0</v>
       </c>
       <c r="Z343" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA343" s="3" t="n">
         <v>1</v>
@@ -38488,10 +38488,10 @@
         <v>0.000561</v>
       </c>
       <c r="Y344" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z344" s="3" t="n">
         <v>-0</v>
-      </c>
-      <c r="Z344" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="AA344" s="3" t="n">
         <v>0</v>
@@ -38791,7 +38791,7 @@
         <v>-0</v>
       </c>
       <c r="Z347" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA347" s="3" t="n">
         <v>0</v>
@@ -39564,10 +39564,10 @@
         <v>0.529801</v>
       </c>
       <c r="Y356" s="3" t="n">
-        <v>0.06324</v>
+        <v>0.122428</v>
       </c>
       <c r="Z356" s="3" t="n">
-        <v>0.065718</v>
+        <v>0.101803</v>
       </c>
       <c r="AB356" s="3" t="n">
         <v>0.636396</v>
@@ -39626,10 +39626,10 @@
         <v>0.445424</v>
       </c>
       <c r="Y358" s="3" t="n">
-        <v>0.319182</v>
+        <v>0.399921</v>
       </c>
       <c r="Z358" s="3" t="n">
-        <v>0.344026</v>
+        <v>0.38208</v>
       </c>
       <c r="AA358" s="3" t="n">
         <v>0.552936</v>
@@ -40001,10 +40001,10 @@
         <v>0.386474</v>
       </c>
       <c r="D8" t="n">
-        <v>0.319182</v>
+        <v>0.399921</v>
       </c>
       <c r="E8" t="n">
-        <v>0.244253</v>
+        <v>0.302156</v>
       </c>
       <c r="F8" t="n">
         <v>0.2988505747126437</v>
@@ -40031,10 +40031,10 @@
         <v>0.216528</v>
       </c>
       <c r="D9" t="n">
-        <v>0.06324</v>
+        <v>0.122428</v>
       </c>
       <c r="E9" t="n">
-        <v>0.05039</v>
+        <v>0.09066100000000001</v>
       </c>
       <c r="F9" t="n">
         <v>0.1641791044776119</v>
@@ -40061,10 +40061,10 @@
         <v>0.41859</v>
       </c>
       <c r="D10" t="n">
-        <v>0.273495</v>
+        <v>0.383985</v>
       </c>
       <c r="E10" t="n">
-        <v>0.220047</v>
+        <v>0.311953</v>
       </c>
       <c r="F10" t="n">
         <v>0.3636363636363636</v>
@@ -40091,10 +40091,10 @@
         <v>0.397421</v>
       </c>
       <c r="D11" t="n">
-        <v>0.344026</v>
+        <v>0.38208</v>
       </c>
       <c r="E11" t="n">
-        <v>0.258237</v>
+        <v>0.284202</v>
       </c>
       <c r="F11" t="n">
         <v>0.3333333333333333</v>
@@ -40121,10 +40121,10 @@
         <v>0.219019</v>
       </c>
       <c r="D12" t="n">
-        <v>0.065718</v>
+        <v>0.101803</v>
       </c>
       <c r="E12" t="n">
-        <v>0.052143</v>
+        <v>0.075336</v>
       </c>
       <c r="F12" t="n">
         <v>0.1716417910447761</v>
@@ -40151,10 +40151,10 @@
         <v>0.43754</v>
       </c>
       <c r="D13" t="n">
-        <v>0.275899</v>
+        <v>0.387852</v>
       </c>
       <c r="E13" t="n">
-        <v>0.222624</v>
+        <v>0.315538</v>
       </c>
       <c r="F13" t="n">
         <v>0.3939393939393939</v>

--- a/EpiRank_改/ERA_result_seqday_d_0.95_loops_305.xlsx
+++ b/EpiRank_改/ERA_result_seqday_d_0.95_loops_305.xlsx
@@ -1485,10 +1485,10 @@
         <v>0.009434</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA7" s="3" t="n">
         <v>2</v>
@@ -2403,10 +2403,10 @@
         <v>0.004698</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA13" s="3" t="n">
         <v>4</v>
@@ -3008,10 +3008,10 @@
         <v>0.008274999999999999</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA17" s="3" t="n">
         <v>4</v>
@@ -3148,10 +3148,10 @@
         <v>0.008586</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA18" s="3" t="n">
         <v>3</v>
@@ -3708,10 +3708,10 @@
         <v>0.004713</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA22" s="3" t="n">
         <v>7</v>
@@ -4098,10 +4098,10 @@
         <v>0.011024</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA25" s="3" t="n">
         <v>8</v>
@@ -4228,10 +4228,10 @@
         <v>0.005408</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA26" s="3" t="n">
         <v>7</v>
@@ -4488,7 +4488,7 @@
         <v>0.007023</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z28" s="3" t="n">
         <v>-0</v>
@@ -5828,10 +5828,10 @@
         <v>0.004917</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA39" s="3" t="n">
         <v>2</v>
@@ -5948,10 +5948,10 @@
         <v>0.007117</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA40" s="3" t="n">
         <v>3</v>
@@ -6788,10 +6788,10 @@
         <v>0.007706</v>
       </c>
       <c r="Y47" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z47" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA47" s="3" t="n">
         <v>2</v>
@@ -7028,10 +7028,10 @@
         <v>0.006149</v>
       </c>
       <c r="Y49" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z49" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA49" s="3" t="n">
         <v>5</v>
@@ -7148,10 +7148,10 @@
         <v>0.004587</v>
       </c>
       <c r="Y50" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z50" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA50" s="3" t="n">
         <v>2</v>
@@ -7388,10 +7388,10 @@
         <v>0.006948</v>
       </c>
       <c r="Y52" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z52" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA52" s="3" t="n">
         <v>3</v>
@@ -7628,10 +7628,10 @@
         <v>0.0015</v>
       </c>
       <c r="Y54" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z54" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA54" s="3" t="n">
         <v>35</v>
@@ -7751,7 +7751,7 @@
         <v>0</v>
       </c>
       <c r="Z55" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA55" s="3" t="n">
         <v>1</v>
@@ -7988,10 +7988,10 @@
         <v>0.005555</v>
       </c>
       <c r="Y57" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z57" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA57" s="3" t="n">
         <v>2</v>
@@ -9548,7 +9548,7 @@
         <v>0.004618</v>
       </c>
       <c r="Y70" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z70" s="3" t="n">
         <v>-0</v>
@@ -9658,10 +9658,10 @@
         <v>0.002491</v>
       </c>
       <c r="Y71" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z71" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA71" s="3" t="n">
         <v>6</v>
@@ -10651,7 +10651,7 @@
         <v>0</v>
       </c>
       <c r="Z80" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA80" s="3" t="n">
         <v>4</v>
@@ -10758,10 +10758,10 @@
         <v>0.003248</v>
       </c>
       <c r="Y81" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z81" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA81" s="3" t="n">
         <v>3</v>
@@ -11088,7 +11088,7 @@
         <v>0.002498</v>
       </c>
       <c r="Y84" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z84" s="3" t="n">
         <v>-0</v>
@@ -12081,7 +12081,7 @@
         <v>-0</v>
       </c>
       <c r="Z93" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA93" s="3" t="n">
         <v>2</v>
@@ -12191,7 +12191,7 @@
         <v>0</v>
       </c>
       <c r="Z94" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA94" s="3" t="n">
         <v>3</v>
@@ -12298,10 +12298,10 @@
         <v>0.003408</v>
       </c>
       <c r="Y95" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z95" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA95" s="3" t="n">
         <v>1</v>
@@ -12518,10 +12518,10 @@
         <v>0.002789</v>
       </c>
       <c r="Y97" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z97" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA97" s="3" t="n">
         <v>1</v>
@@ -12628,10 +12628,10 @@
         <v>0.003197</v>
       </c>
       <c r="Y98" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z98" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA98" s="3" t="n">
         <v>1</v>
@@ -13398,10 +13398,10 @@
         <v>0.003781</v>
       </c>
       <c r="Y105" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z105" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA105" s="3" t="n">
         <v>0</v>
@@ -14388,10 +14388,10 @@
         <v>0.002496</v>
       </c>
       <c r="Y114" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z114" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA114" s="3" t="n">
         <v>1</v>
@@ -14608,10 +14608,10 @@
         <v>0.002715</v>
       </c>
       <c r="Y116" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z116" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA116" s="3" t="n">
         <v>1</v>
@@ -14828,10 +14828,10 @@
         <v>0.002833</v>
       </c>
       <c r="Y118" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z118" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA118" s="3" t="n">
         <v>0</v>
@@ -15048,7 +15048,7 @@
         <v>0.003882</v>
       </c>
       <c r="Y120" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z120" s="3" t="n">
         <v>-0</v>
@@ -15271,7 +15271,7 @@
         <v>0</v>
       </c>
       <c r="Z122" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA122" s="3" t="n">
         <v>2</v>
@@ -15378,10 +15378,10 @@
         <v>0.00191</v>
       </c>
       <c r="Y123" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z123" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA123" s="3" t="n">
         <v>1</v>
@@ -16368,10 +16368,10 @@
         <v>0.002787</v>
       </c>
       <c r="Y132" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z132" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA132" s="3" t="n">
         <v>2</v>
@@ -16701,7 +16701,7 @@
         <v>0</v>
       </c>
       <c r="Z135" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA135" s="3" t="n">
         <v>0</v>
@@ -17358,7 +17358,7 @@
         <v>0.002448</v>
       </c>
       <c r="Y141" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z141" s="3" t="n">
         <v>0</v>
@@ -17798,7 +17798,7 @@
         <v>0.001951</v>
       </c>
       <c r="Y145" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z145" s="3" t="n">
         <v>-0</v>
@@ -18128,10 +18128,10 @@
         <v>0.002964</v>
       </c>
       <c r="Y148" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z148" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA148" s="3" t="n">
         <v>3</v>
@@ -18461,7 +18461,7 @@
         <v>-0</v>
       </c>
       <c r="Z151" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA151" s="3" t="n">
         <v>0</v>
@@ -18678,10 +18678,10 @@
         <v>0.001714</v>
       </c>
       <c r="Y153" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z153" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA153" s="3" t="n">
         <v>2</v>
@@ -18898,10 +18898,10 @@
         <v>0.001295</v>
       </c>
       <c r="Y155" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z155" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA155" s="3" t="n">
         <v>0</v>
@@ -19008,10 +19008,10 @@
         <v>0.002578</v>
       </c>
       <c r="Y156" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z156" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA156" s="3" t="n">
         <v>0</v>
@@ -19118,10 +19118,10 @@
         <v>0.002604</v>
       </c>
       <c r="Y157" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z157" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA157" s="3" t="n">
         <v>7</v>
@@ -19231,7 +19231,7 @@
         <v>0</v>
       </c>
       <c r="Z158" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA158" s="3" t="n">
         <v>1</v>
@@ -19338,7 +19338,7 @@
         <v>0.002147</v>
       </c>
       <c r="Y159" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z159" s="3" t="n">
         <v>-0</v>
@@ -19448,10 +19448,10 @@
         <v>0.002491</v>
       </c>
       <c r="Y160" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z160" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA160" s="3" t="n">
         <v>2</v>
@@ -19671,7 +19671,7 @@
         <v>0</v>
       </c>
       <c r="Z162" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA162" s="3" t="n">
         <v>1</v>
@@ -19891,7 +19891,7 @@
         <v>0</v>
       </c>
       <c r="Z164" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA164" s="3" t="n">
         <v>0</v>
@@ -20001,7 +20001,7 @@
         <v>0</v>
       </c>
       <c r="Z165" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA165" s="3" t="n">
         <v>0</v>
@@ -20218,10 +20218,10 @@
         <v>0.001621</v>
       </c>
       <c r="Y167" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z167" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA167" s="3" t="n">
         <v>2</v>
@@ -20551,7 +20551,7 @@
         <v>0</v>
       </c>
       <c r="Z170" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA170" s="3" t="n">
         <v>5</v>
@@ -20768,10 +20768,10 @@
         <v>0.001501</v>
       </c>
       <c r="Y172" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z172" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA172" s="3" t="n">
         <v>1</v>
@@ -20878,10 +20878,10 @@
         <v>0.004587</v>
       </c>
       <c r="Y173" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z173" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA173" s="3" t="n">
         <v>0</v>
@@ -20991,7 +20991,7 @@
         <v>-0</v>
       </c>
       <c r="Z174" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA174" s="3" t="n">
         <v>2</v>
@@ -21098,10 +21098,10 @@
         <v>0.001399</v>
       </c>
       <c r="Y175" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z175" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA175" s="3" t="n">
         <v>1</v>
@@ -21208,10 +21208,10 @@
         <v>0.003002</v>
       </c>
       <c r="Y176" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z176" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA176" s="3" t="n">
         <v>0</v>
@@ -21321,7 +21321,7 @@
         <v>0</v>
       </c>
       <c r="Z177" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA177" s="3" t="n">
         <v>2</v>
@@ -21651,7 +21651,7 @@
         <v>0</v>
       </c>
       <c r="Z180" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA180" s="3" t="n">
         <v>1</v>
@@ -21761,7 +21761,7 @@
         <v>0</v>
       </c>
       <c r="Z181" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA181" s="3" t="n">
         <v>3</v>
@@ -21868,10 +21868,10 @@
         <v>0.001797</v>
       </c>
       <c r="Y182" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z182" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA182" s="3" t="n">
         <v>0</v>
@@ -22311,7 +22311,7 @@
         <v>-0</v>
       </c>
       <c r="Z186" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA186" s="3" t="n">
         <v>0</v>
@@ -22531,7 +22531,7 @@
         <v>0</v>
       </c>
       <c r="Z188" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA188" s="3" t="n">
         <v>0</v>
@@ -22861,7 +22861,7 @@
         <v>0</v>
       </c>
       <c r="Z191" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA191" s="3" t="n">
         <v>0</v>
@@ -23191,7 +23191,7 @@
         <v>-0</v>
       </c>
       <c r="Z194" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA194" s="3" t="n">
         <v>1</v>
@@ -23408,10 +23408,10 @@
         <v>0.002813</v>
       </c>
       <c r="Y196" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z196" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA196" s="3" t="n">
         <v>1</v>
@@ -23518,10 +23518,10 @@
         <v>0.002087</v>
       </c>
       <c r="Y197" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z197" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA197" s="3" t="n">
         <v>0</v>
@@ -23628,7 +23628,7 @@
         <v>0.001081</v>
       </c>
       <c r="Y198" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z198" s="3" t="n">
         <v>-0</v>
@@ -23958,7 +23958,7 @@
         <v>0.002161</v>
       </c>
       <c r="Y201" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z201" s="3" t="n">
         <v>-0</v>
@@ -24511,7 +24511,7 @@
         <v>0</v>
       </c>
       <c r="Z206" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA206" s="3" t="n">
         <v>1</v>
@@ -25171,7 +25171,7 @@
         <v>0</v>
       </c>
       <c r="Z212" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA212" s="3" t="n">
         <v>0</v>
@@ -25278,10 +25278,10 @@
         <v>0.001686</v>
       </c>
       <c r="Y213" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z213" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA213" s="3" t="n">
         <v>1</v>
@@ -25611,7 +25611,7 @@
         <v>0</v>
       </c>
       <c r="Z216" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA216" s="3" t="n">
         <v>2</v>
@@ -25828,10 +25828,10 @@
         <v>0.002238</v>
       </c>
       <c r="Y218" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z218" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA218" s="3" t="n">
         <v>0</v>
@@ -25938,10 +25938,10 @@
         <v>0.001152</v>
       </c>
       <c r="Y219" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z219" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA219" s="3" t="n">
         <v>0</v>
@@ -26161,7 +26161,7 @@
         <v>0</v>
       </c>
       <c r="Z221" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA221" s="3" t="n">
         <v>2</v>
@@ -26271,7 +26271,7 @@
         <v>0</v>
       </c>
       <c r="Z222" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA222" s="3" t="n">
         <v>1</v>
@@ -26491,7 +26491,7 @@
         <v>0</v>
       </c>
       <c r="Z224" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA224" s="3" t="n">
         <v>2</v>
@@ -26791,7 +26791,7 @@
         <v>0</v>
       </c>
       <c r="Z227" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA227" s="3" t="n">
         <v>0</v>
@@ -27288,10 +27288,10 @@
         <v>0.00185</v>
       </c>
       <c r="Y232" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z232" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA232" s="3" t="n">
         <v>2</v>
@@ -27391,7 +27391,7 @@
         <v>0</v>
       </c>
       <c r="Z233" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA233" s="3" t="n">
         <v>0</v>
@@ -27488,7 +27488,7 @@
         <v>0.001592</v>
       </c>
       <c r="Y234" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z234" s="3" t="n">
         <v>-0</v>
@@ -27588,7 +27588,7 @@
         <v>0.000995</v>
       </c>
       <c r="Y235" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z235" s="3" t="n">
         <v>-0</v>
@@ -27988,7 +27988,7 @@
         <v>0.00079</v>
       </c>
       <c r="Y239" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z239" s="3" t="n">
         <v>0</v>
@@ -28088,7 +28088,7 @@
         <v>0.00144</v>
       </c>
       <c r="Y240" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z240" s="3" t="n">
         <v>-0</v>
@@ -28491,7 +28491,7 @@
         <v>0</v>
       </c>
       <c r="Z244" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA244" s="3" t="n">
         <v>1</v>
@@ -29088,10 +29088,10 @@
         <v>0.001577</v>
       </c>
       <c r="Y250" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z250" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA250" s="3" t="n">
         <v>0</v>
@@ -29188,7 +29188,7 @@
         <v>0.001556</v>
       </c>
       <c r="Y251" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z251" s="3" t="n">
         <v>-0</v>
@@ -29391,7 +29391,7 @@
         <v>0</v>
       </c>
       <c r="Z253" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA253" s="3" t="n">
         <v>0</v>
@@ -29791,7 +29791,7 @@
         <v>-0</v>
       </c>
       <c r="Z257" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA257" s="3" t="n">
         <v>0</v>
@@ -30088,10 +30088,10 @@
         <v>0.00143</v>
       </c>
       <c r="Y260" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z260" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA260" s="3" t="n">
         <v>0</v>
@@ -30288,7 +30288,7 @@
         <v>0.001019</v>
       </c>
       <c r="Y262" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z262" s="3" t="n">
         <v>-0</v>
@@ -30388,10 +30388,10 @@
         <v>0.000785</v>
       </c>
       <c r="Y263" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z263" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA263" s="3" t="n">
         <v>0</v>
@@ -30588,7 +30588,7 @@
         <v>0.001509</v>
       </c>
       <c r="Y265" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z265" s="3" t="n">
         <v>-0</v>
@@ -30788,10 +30788,10 @@
         <v>0.001032</v>
       </c>
       <c r="Y267" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z267" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA267" s="3" t="n">
         <v>0</v>
@@ -30888,10 +30888,10 @@
         <v>0.001148</v>
       </c>
       <c r="Y268" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z268" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA268" s="3" t="n">
         <v>0</v>
@@ -30988,7 +30988,7 @@
         <v>0.001296</v>
       </c>
       <c r="Y269" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z269" s="3" t="n">
         <v>-0</v>
@@ -31188,7 +31188,7 @@
         <v>0.001877</v>
       </c>
       <c r="Y271" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z271" s="3" t="n">
         <v>0</v>
@@ -31288,10 +31288,10 @@
         <v>0.001118</v>
       </c>
       <c r="Y272" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z272" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA272" s="3" t="n">
         <v>0</v>
@@ -31591,7 +31591,7 @@
         <v>0</v>
       </c>
       <c r="Z275" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA275" s="3" t="n">
         <v>1</v>
@@ -31788,7 +31788,7 @@
         <v>0.001352</v>
       </c>
       <c r="Y277" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z277" s="3" t="n">
         <v>-0</v>
@@ -32491,7 +32491,7 @@
         <v>-0</v>
       </c>
       <c r="Z284" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA284" s="3" t="n">
         <v>0</v>
@@ -32691,7 +32691,7 @@
         <v>0</v>
       </c>
       <c r="Z286" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA286" s="3" t="n">
         <v>1</v>
@@ -32988,7 +32988,7 @@
         <v>0.00134</v>
       </c>
       <c r="Y289" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z289" s="3" t="n">
         <v>-0</v>
@@ -33088,10 +33088,10 @@
         <v>0.001506</v>
       </c>
       <c r="Y290" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z290" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA290" s="3" t="n">
         <v>2</v>
@@ -33788,10 +33788,10 @@
         <v>0.001133</v>
       </c>
       <c r="Y297" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z297" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA297" s="3" t="n">
         <v>0</v>
@@ -34091,7 +34091,7 @@
         <v>0</v>
       </c>
       <c r="Z300" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA300" s="3" t="n">
         <v>0</v>
@@ -34491,7 +34491,7 @@
         <v>-0</v>
       </c>
       <c r="Z304" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA304" s="3" t="n">
         <v>0</v>
@@ -34588,7 +34588,7 @@
         <v>0.000908</v>
       </c>
       <c r="Y305" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z305" s="3" t="n">
         <v>0</v>
@@ -35191,7 +35191,7 @@
         <v>0</v>
       </c>
       <c r="Z311" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA311" s="3" t="n">
         <v>0</v>
@@ -35288,7 +35288,7 @@
         <v>0.000803</v>
       </c>
       <c r="Y312" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z312" s="3" t="n">
         <v>0</v>
@@ -35391,7 +35391,7 @@
         <v>-0</v>
       </c>
       <c r="Z313" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA313" s="3" t="n">
         <v>0</v>
@@ -35691,7 +35691,7 @@
         <v>0</v>
       </c>
       <c r="Z316" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA316" s="3" t="n">
         <v>0</v>
@@ -35791,7 +35791,7 @@
         <v>0</v>
       </c>
       <c r="Z317" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA317" s="3" t="n">
         <v>1</v>
@@ -36191,7 +36191,7 @@
         <v>-0</v>
       </c>
       <c r="Z321" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA321" s="3" t="n">
         <v>0</v>
@@ -36391,7 +36391,7 @@
         <v>0</v>
       </c>
       <c r="Z323" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA323" s="3" t="n">
         <v>3</v>
@@ -36588,10 +36588,10 @@
         <v>0.00087</v>
       </c>
       <c r="Y325" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z325" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA325" s="3" t="n">
         <v>0</v>
@@ -37188,7 +37188,7 @@
         <v>0.000763</v>
       </c>
       <c r="Y331" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z331" s="3" t="n">
         <v>0</v>
@@ -37791,7 +37791,7 @@
         <v>0</v>
       </c>
       <c r="Z337" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA337" s="3" t="n">
         <v>0</v>
@@ -38188,10 +38188,10 @@
         <v>0.001203</v>
       </c>
       <c r="Y341" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z341" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA341" s="3" t="n">
         <v>0</v>
@@ -38388,10 +38388,10 @@
         <v>0.000725</v>
       </c>
       <c r="Y343" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z343" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA343" s="3" t="n">
         <v>1</v>
@@ -38491,7 +38491,7 @@
         <v>0</v>
       </c>
       <c r="Z344" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA344" s="3" t="n">
         <v>0</v>
@@ -38788,10 +38788,10 @@
         <v>0.000592</v>
       </c>
       <c r="Y347" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z347" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA347" s="3" t="n">
         <v>0</v>
@@ -39564,10 +39564,10 @@
         <v>0.529801</v>
       </c>
       <c r="Y356" s="3" t="n">
-        <v>0.122428</v>
+        <v>0.13864</v>
       </c>
       <c r="Z356" s="3" t="n">
-        <v>0.101803</v>
+        <v>0.09328599999999999</v>
       </c>
       <c r="AB356" s="3" t="n">
         <v>0.636396</v>
@@ -39626,10 +39626,10 @@
         <v>0.445424</v>
       </c>
       <c r="Y358" s="3" t="n">
-        <v>0.399921</v>
+        <v>0.388775</v>
       </c>
       <c r="Z358" s="3" t="n">
-        <v>0.38208</v>
+        <v>0.357447</v>
       </c>
       <c r="AA358" s="3" t="n">
         <v>0.552936</v>
@@ -40001,10 +40001,10 @@
         <v>0.386474</v>
       </c>
       <c r="D8" t="n">
-        <v>0.399921</v>
+        <v>0.388775</v>
       </c>
       <c r="E8" t="n">
-        <v>0.302156</v>
+        <v>0.303443</v>
       </c>
       <c r="F8" t="n">
         <v>0.2988505747126437</v>
@@ -40031,10 +40031,10 @@
         <v>0.216528</v>
       </c>
       <c r="D9" t="n">
-        <v>0.122428</v>
+        <v>0.13864</v>
       </c>
       <c r="E9" t="n">
-        <v>0.09066100000000001</v>
+        <v>0.105196</v>
       </c>
       <c r="F9" t="n">
         <v>0.1641791044776119</v>
@@ -40061,10 +40061,10 @@
         <v>0.41859</v>
       </c>
       <c r="D10" t="n">
-        <v>0.383985</v>
+        <v>0.34906</v>
       </c>
       <c r="E10" t="n">
-        <v>0.311953</v>
+        <v>0.282662</v>
       </c>
       <c r="F10" t="n">
         <v>0.3636363636363636</v>
@@ -40091,10 +40091,10 @@
         <v>0.397421</v>
       </c>
       <c r="D11" t="n">
-        <v>0.38208</v>
+        <v>0.357447</v>
       </c>
       <c r="E11" t="n">
-        <v>0.284202</v>
+        <v>0.272114</v>
       </c>
       <c r="F11" t="n">
         <v>0.3333333333333333</v>
@@ -40121,10 +40121,10 @@
         <v>0.219019</v>
       </c>
       <c r="D12" t="n">
-        <v>0.101803</v>
+        <v>0.09328599999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>0.075336</v>
+        <v>0.06843</v>
       </c>
       <c r="F12" t="n">
         <v>0.1716417910447761</v>
@@ -40151,10 +40151,10 @@
         <v>0.43754</v>
       </c>
       <c r="D13" t="n">
-        <v>0.387852</v>
+        <v>0.354132</v>
       </c>
       <c r="E13" t="n">
-        <v>0.315538</v>
+        <v>0.287591</v>
       </c>
       <c r="F13" t="n">
         <v>0.3939393939393939</v>

--- a/EpiRank_改/ERA_result_seqday_d_0.95_loops_305.xlsx
+++ b/EpiRank_改/ERA_result_seqday_d_0.95_loops_305.xlsx
@@ -1024,10 +1024,10 @@
         <v>0.012871</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA4" s="3" t="n">
         <v>11</v>
@@ -1179,10 +1179,10 @@
         <v>0.011776</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA5" s="3" t="n">
         <v>11</v>
@@ -2093,10 +2093,10 @@
         <v>0.01153</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA11" s="3" t="n">
         <v>4</v>
@@ -2248,10 +2248,10 @@
         <v>0.00662</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA12" s="3" t="n">
         <v>6</v>
@@ -3008,10 +3008,10 @@
         <v>0.008288999999999999</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA17" s="3" t="n">
         <v>4</v>
@@ -3148,10 +3148,10 @@
         <v>0.008602</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA18" s="3" t="n">
         <v>3</v>
@@ -3708,10 +3708,10 @@
         <v>0.004719</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA22" s="3" t="n">
         <v>7</v>
@@ -4098,10 +4098,10 @@
         <v>0.011055</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA25" s="3" t="n">
         <v>8</v>
@@ -4358,10 +4358,10 @@
         <v>0.007025</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z27" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA27" s="3" t="n">
         <v>8</v>
@@ -4491,7 +4491,7 @@
         <v>-0</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA28" s="3" t="n">
         <v>7</v>
@@ -6678,10 +6678,10 @@
         <v>0.005847</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA46" s="3" t="n">
         <v>0</v>
@@ -7158,10 +7158,10 @@
         <v>0.0046</v>
       </c>
       <c r="Y50" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z50" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA50" s="3" t="n">
         <v>2</v>
@@ -7398,10 +7398,10 @@
         <v>0.006967</v>
       </c>
       <c r="Y52" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z52" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA52" s="3" t="n">
         <v>3</v>
@@ -7638,10 +7638,10 @@
         <v>0.001504</v>
       </c>
       <c r="Y54" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z54" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA54" s="3" t="n">
         <v>35</v>
@@ -7761,7 +7761,7 @@
         <v>0</v>
       </c>
       <c r="Z55" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA55" s="3" t="n">
         <v>1</v>
@@ -8118,10 +8118,10 @@
         <v>0.005539</v>
       </c>
       <c r="Y58" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z58" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA58" s="3" t="n">
         <v>2</v>
@@ -8598,10 +8598,10 @@
         <v>0.002652</v>
       </c>
       <c r="Y62" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z62" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA62" s="3" t="n">
         <v>4</v>
@@ -8958,10 +8958,10 @@
         <v>0.006417</v>
       </c>
       <c r="Y65" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z65" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA65" s="3" t="n">
         <v>4</v>
@@ -10561,7 +10561,7 @@
         <v>0</v>
       </c>
       <c r="Z79" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA79" s="3" t="n">
         <v>6</v>
@@ -10778,10 +10778,10 @@
         <v>0.003257</v>
       </c>
       <c r="Y81" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z81" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA81" s="3" t="n">
         <v>3</v>
@@ -10891,7 +10891,7 @@
         <v>0</v>
       </c>
       <c r="Z82" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA82" s="3" t="n">
         <v>1</v>
@@ -11218,10 +11218,10 @@
         <v>0.002491</v>
       </c>
       <c r="Y85" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z85" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA85" s="3" t="n">
         <v>0</v>
@@ -11548,10 +11548,10 @@
         <v>0.00305</v>
       </c>
       <c r="Y88" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z88" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA88" s="3" t="n">
         <v>1</v>
@@ -12098,10 +12098,10 @@
         <v>0.004367</v>
       </c>
       <c r="Y93" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z93" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA93" s="3" t="n">
         <v>0</v>
@@ -12208,10 +12208,10 @@
         <v>0.001993</v>
       </c>
       <c r="Y94" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z94" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA94" s="3" t="n">
         <v>2</v>
@@ -12318,10 +12318,10 @@
         <v>0.002955</v>
       </c>
       <c r="Y95" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z95" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA95" s="3" t="n">
         <v>3</v>
@@ -12428,7 +12428,7 @@
         <v>0.003417</v>
       </c>
       <c r="Y96" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z96" s="3" t="n">
         <v>-0</v>
@@ -13418,10 +13418,10 @@
         <v>0.003378</v>
       </c>
       <c r="Y105" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z105" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA105" s="3" t="n">
         <v>2</v>
@@ -13748,10 +13748,10 @@
         <v>0.002019</v>
       </c>
       <c r="Y108" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z108" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA108" s="3" t="n">
         <v>3</v>
@@ -14078,10 +14078,10 @@
         <v>0.003698</v>
       </c>
       <c r="Y111" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z111" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA111" s="3" t="n">
         <v>0</v>
@@ -14631,7 +14631,7 @@
         <v>0</v>
       </c>
       <c r="Z116" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA116" s="3" t="n">
         <v>1</v>
@@ -14848,10 +14848,10 @@
         <v>0.002841</v>
       </c>
       <c r="Y118" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z118" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA118" s="3" t="n">
         <v>0</v>
@@ -15068,10 +15068,10 @@
         <v>0.003887</v>
       </c>
       <c r="Y120" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z120" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA120" s="3" t="n">
         <v>0</v>
@@ -15621,7 +15621,7 @@
         <v>0</v>
       </c>
       <c r="Z125" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA125" s="3" t="n">
         <v>1</v>
@@ -16608,10 +16608,10 @@
         <v>0.002601</v>
       </c>
       <c r="Y134" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z134" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA134" s="3" t="n">
         <v>0</v>
@@ -16718,10 +16718,10 @@
         <v>0.002587</v>
       </c>
       <c r="Y135" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z135" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA135" s="3" t="n">
         <v>0</v>
@@ -16938,10 +16938,10 @@
         <v>0.003318</v>
       </c>
       <c r="Y137" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z137" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA137" s="3" t="n">
         <v>3</v>
@@ -17818,10 +17818,10 @@
         <v>0.001814</v>
       </c>
       <c r="Y145" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z145" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA145" s="3" t="n">
         <v>1</v>
@@ -17928,7 +17928,7 @@
         <v>0.001956</v>
       </c>
       <c r="Y146" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z146" s="3" t="n">
         <v>-0</v>
@@ -18481,7 +18481,7 @@
         <v>0</v>
       </c>
       <c r="Z151" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA151" s="3" t="n">
         <v>0</v>
@@ -18698,10 +18698,10 @@
         <v>0.001719</v>
       </c>
       <c r="Y153" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z153" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA153" s="3" t="n">
         <v>2</v>
@@ -18808,10 +18808,10 @@
         <v>0.002941</v>
       </c>
       <c r="Y154" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z154" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA154" s="3" t="n">
         <v>3</v>
@@ -19028,10 +19028,10 @@
         <v>0.001298</v>
       </c>
       <c r="Y156" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z156" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA156" s="3" t="n">
         <v>0</v>
@@ -19468,10 +19468,10 @@
         <v>0.002153</v>
       </c>
       <c r="Y160" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z160" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA160" s="3" t="n">
         <v>1</v>
@@ -19801,7 +19801,7 @@
         <v>0</v>
       </c>
       <c r="Z163" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA163" s="3" t="n">
         <v>1</v>
@@ -20018,10 +20018,10 @@
         <v>0.001311</v>
       </c>
       <c r="Y165" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z165" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA165" s="3" t="n">
         <v>0</v>
@@ -20241,7 +20241,7 @@
         <v>0</v>
       </c>
       <c r="Z167" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA167" s="3" t="n">
         <v>0</v>
@@ -20348,10 +20348,10 @@
         <v>0.001626</v>
       </c>
       <c r="Y168" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z168" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA168" s="3" t="n">
         <v>2</v>
@@ -20788,10 +20788,10 @@
         <v>0.002439</v>
       </c>
       <c r="Y172" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z172" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA172" s="3" t="n">
         <v>1</v>
@@ -20898,10 +20898,10 @@
         <v>0.001505</v>
       </c>
       <c r="Y173" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z173" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA173" s="3" t="n">
         <v>1</v>
@@ -21008,7 +21008,7 @@
         <v>0.001403</v>
       </c>
       <c r="Y174" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z174" s="3" t="n">
         <v>0</v>
@@ -21228,10 +21228,10 @@
         <v>0.001968</v>
       </c>
       <c r="Y176" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z176" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA176" s="3" t="n">
         <v>2</v>
@@ -21451,7 +21451,7 @@
         <v>0</v>
       </c>
       <c r="Z178" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA178" s="3" t="n">
         <v>0</v>
@@ -21668,10 +21668,10 @@
         <v>0.001239</v>
       </c>
       <c r="Y180" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z180" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA180" s="3" t="n">
         <v>1</v>
@@ -21778,10 +21778,10 @@
         <v>0.001802</v>
       </c>
       <c r="Y181" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z181" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA181" s="3" t="n">
         <v>0</v>
@@ -21888,10 +21888,10 @@
         <v>0.000973</v>
       </c>
       <c r="Y182" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z182" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA182" s="3" t="n">
         <v>3</v>
@@ -22331,7 +22331,7 @@
         <v>0</v>
       </c>
       <c r="Z186" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA186" s="3" t="n">
         <v>0</v>
@@ -22548,10 +22548,10 @@
         <v>0.002549</v>
       </c>
       <c r="Y188" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z188" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA188" s="3" t="n">
         <v>1</v>
@@ -22768,10 +22768,10 @@
         <v>0.001262</v>
       </c>
       <c r="Y190" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z190" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA190" s="3" t="n">
         <v>1</v>
@@ -23101,7 +23101,7 @@
         <v>0</v>
       </c>
       <c r="Z193" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA193" s="3" t="n">
         <v>1</v>
@@ -23431,7 +23431,7 @@
         <v>0</v>
       </c>
       <c r="Z196" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA196" s="3" t="n">
         <v>0</v>
@@ -23758,10 +23758,10 @@
         <v>0.002167</v>
       </c>
       <c r="Y199" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z199" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA199" s="3" t="n">
         <v>0</v>
@@ -23871,7 +23871,7 @@
         <v>0</v>
       </c>
       <c r="Z200" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA200" s="3" t="n">
         <v>0</v>
@@ -24091,7 +24091,7 @@
         <v>-0</v>
       </c>
       <c r="Z202" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA202" s="3" t="n">
         <v>6</v>
@@ -24528,10 +24528,10 @@
         <v>0.001369</v>
       </c>
       <c r="Y206" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z206" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA206" s="3" t="n">
         <v>3</v>
@@ -24748,10 +24748,10 @@
         <v>0.001165</v>
       </c>
       <c r="Y208" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z208" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA208" s="3" t="n">
         <v>1</v>
@@ -24861,7 +24861,7 @@
         <v>0</v>
       </c>
       <c r="Z209" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA209" s="3" t="n">
         <v>0</v>
@@ -24968,7 +24968,7 @@
         <v>0.0008140000000000001</v>
       </c>
       <c r="Y210" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z210" s="3" t="n">
         <v>-0</v>
@@ -25081,7 +25081,7 @@
         <v>-0</v>
       </c>
       <c r="Z211" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA211" s="3" t="n">
         <v>1</v>
@@ -25411,7 +25411,7 @@
         <v>0</v>
       </c>
       <c r="Z214" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA214" s="3" t="n">
         <v>0</v>
@@ -25631,7 +25631,7 @@
         <v>-0</v>
       </c>
       <c r="Z216" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA216" s="3" t="n">
         <v>5</v>
@@ -25738,10 +25738,10 @@
         <v>0.002244</v>
       </c>
       <c r="Y217" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z217" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA217" s="3" t="n">
         <v>0</v>
@@ -25961,7 +25961,7 @@
         <v>0</v>
       </c>
       <c r="Z219" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA219" s="3" t="n">
         <v>2</v>
@@ -26481,7 +26481,7 @@
         <v>0</v>
       </c>
       <c r="Z224" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA224" s="3" t="n">
         <v>1</v>
@@ -26781,7 +26781,7 @@
         <v>0</v>
       </c>
       <c r="Z227" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA227" s="3" t="n">
         <v>3</v>
@@ -26981,7 +26981,7 @@
         <v>0</v>
       </c>
       <c r="Z229" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA229" s="3" t="n">
         <v>2</v>
@@ -27078,7 +27078,7 @@
         <v>0.000868</v>
       </c>
       <c r="Y230" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z230" s="3" t="n">
         <v>-0</v>
@@ -27178,10 +27178,10 @@
         <v>0.001353</v>
       </c>
       <c r="Y231" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z231" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA231" s="3" t="n">
         <v>0</v>
@@ -27278,7 +27278,7 @@
         <v>0.001597</v>
       </c>
       <c r="Y232" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z232" s="3" t="n">
         <v>-0</v>
@@ -27378,10 +27378,10 @@
         <v>0.001385</v>
       </c>
       <c r="Y233" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z233" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA233" s="3" t="n">
         <v>0</v>
@@ -27581,7 +27581,7 @@
         <v>0</v>
       </c>
       <c r="Z235" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA235" s="3" t="n">
         <v>0</v>
@@ -27678,10 +27678,10 @@
         <v>0.001312</v>
       </c>
       <c r="Y236" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z236" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA236" s="3" t="n">
         <v>0</v>
@@ -27778,10 +27778,10 @@
         <v>0.000673</v>
       </c>
       <c r="Y237" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z237" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA237" s="3" t="n">
         <v>2</v>
@@ -27878,10 +27878,10 @@
         <v>0.001444</v>
       </c>
       <c r="Y238" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z238" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA238" s="3" t="n">
         <v>0</v>
@@ -28078,10 +28078,10 @@
         <v>0.002065</v>
       </c>
       <c r="Y240" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z240" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA240" s="3" t="n">
         <v>0</v>
@@ -28181,7 +28181,7 @@
         <v>-0</v>
       </c>
       <c r="Z241" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA241" s="3" t="n">
         <v>6</v>
@@ -28278,10 +28278,10 @@
         <v>0.000784</v>
       </c>
       <c r="Y242" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z242" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA242" s="3" t="n">
         <v>1</v>
@@ -28381,7 +28381,7 @@
         <v>0</v>
       </c>
       <c r="Z243" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA243" s="3" t="n">
         <v>1</v>
@@ -28578,10 +28578,10 @@
         <v>0.001251</v>
       </c>
       <c r="Y245" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z245" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA245" s="3" t="n">
         <v>0</v>
@@ -28778,7 +28778,7 @@
         <v>0.002004</v>
       </c>
       <c r="Y247" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z247" s="3" t="n">
         <v>-0</v>
@@ -28881,7 +28881,7 @@
         <v>0</v>
       </c>
       <c r="Z248" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA248" s="3" t="n">
         <v>0</v>
@@ -28978,10 +28978,10 @@
         <v>0.001581</v>
       </c>
       <c r="Y249" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z249" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA249" s="3" t="n">
         <v>0</v>
@@ -29081,7 +29081,7 @@
         <v>0</v>
       </c>
       <c r="Z250" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA250" s="3" t="n">
         <v>2</v>
@@ -29178,10 +29178,10 @@
         <v>0.001668</v>
       </c>
       <c r="Y251" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z251" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA251" s="3" t="n">
         <v>0</v>
@@ -29278,10 +29278,10 @@
         <v>0.001549</v>
       </c>
       <c r="Y252" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z252" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA252" s="3" t="n">
         <v>0</v>
@@ -29578,7 +29578,7 @@
         <v>0.001518</v>
       </c>
       <c r="Y255" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z255" s="3" t="n">
         <v>0</v>
@@ -29781,7 +29781,7 @@
         <v>0</v>
       </c>
       <c r="Z257" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA257" s="3" t="n">
         <v>1</v>
@@ -29878,10 +29878,10 @@
         <v>0.001639</v>
       </c>
       <c r="Y258" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z258" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA258" s="3" t="n">
         <v>0</v>
@@ -30078,10 +30078,10 @@
         <v>0.001409</v>
       </c>
       <c r="Y260" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z260" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA260" s="3" t="n">
         <v>0</v>
@@ -30381,7 +30381,7 @@
         <v>0</v>
       </c>
       <c r="Z263" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA263" s="3" t="n">
         <v>0</v>
@@ -30478,10 +30478,10 @@
         <v>0.000786</v>
       </c>
       <c r="Y264" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z264" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA264" s="3" t="n">
         <v>0</v>
@@ -30678,10 +30678,10 @@
         <v>0.001035</v>
       </c>
       <c r="Y266" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z266" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA266" s="3" t="n">
         <v>0</v>
@@ -30881,7 +30881,7 @@
         <v>-0</v>
       </c>
       <c r="Z268" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA268" s="3" t="n">
         <v>1</v>
@@ -31081,7 +31081,7 @@
         <v>-0</v>
       </c>
       <c r="Z270" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA270" s="3" t="n">
         <v>0</v>
@@ -31181,7 +31181,7 @@
         <v>0</v>
       </c>
       <c r="Z271" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA271" s="3" t="n">
         <v>0</v>
@@ -31478,7 +31478,7 @@
         <v>0.000806</v>
       </c>
       <c r="Y274" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z274" s="3" t="n">
         <v>-0</v>
@@ -31678,10 +31678,10 @@
         <v>0.001356</v>
       </c>
       <c r="Y276" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z276" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA276" s="3" t="n">
         <v>0</v>
@@ -32078,10 +32078,10 @@
         <v>0.000873</v>
       </c>
       <c r="Y280" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z280" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA280" s="3" t="n">
         <v>1</v>
@@ -32181,7 +32181,7 @@
         <v>-0</v>
       </c>
       <c r="Z281" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA281" s="3" t="n">
         <v>0</v>
@@ -32278,10 +32278,10 @@
         <v>0.000885</v>
       </c>
       <c r="Y282" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z282" s="3" t="n">
         <v>-0</v>
-      </c>
-      <c r="Z282" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="AA282" s="3" t="n">
         <v>0</v>
@@ -32478,7 +32478,7 @@
         <v>0.00095</v>
       </c>
       <c r="Y284" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z284" s="3" t="n">
         <v>0</v>
@@ -32581,7 +32581,7 @@
         <v>0</v>
       </c>
       <c r="Z285" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA285" s="3" t="n">
         <v>1</v>
@@ -32778,7 +32778,7 @@
         <v>0.003156</v>
       </c>
       <c r="Y287" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z287" s="3" t="n">
         <v>0</v>
@@ -32878,10 +32878,10 @@
         <v>0.001343</v>
       </c>
       <c r="Y288" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z288" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA288" s="3" t="n">
         <v>0</v>
@@ -33278,10 +33278,10 @@
         <v>0.001776</v>
       </c>
       <c r="Y292" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z292" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA292" s="3" t="n">
         <v>1</v>
@@ -33678,10 +33678,10 @@
         <v>0.001136</v>
       </c>
       <c r="Y296" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z296" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA296" s="3" t="n">
         <v>0</v>
@@ -34481,7 +34481,7 @@
         <v>0</v>
       </c>
       <c r="Z304" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA304" s="3" t="n">
         <v>0</v>
@@ -34778,7 +34778,7 @@
         <v>0.000775</v>
       </c>
       <c r="Y307" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z307" s="3" t="n">
         <v>-0</v>
@@ -35078,10 +35078,10 @@
         <v>0.000922</v>
       </c>
       <c r="Y310" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z310" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA310" s="3" t="n">
         <v>0</v>
@@ -35181,7 +35181,7 @@
         <v>-0</v>
       </c>
       <c r="Z311" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA311" s="3" t="n">
         <v>0</v>
@@ -35278,7 +35278,7 @@
         <v>0.000802</v>
       </c>
       <c r="Y312" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z312" s="3" t="n">
         <v>-0</v>
@@ -35681,7 +35681,7 @@
         <v>0</v>
       </c>
       <c r="Z316" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA316" s="3" t="n">
         <v>1</v>
@@ -35981,7 +35981,7 @@
         <v>0</v>
       </c>
       <c r="Z319" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA319" s="3" t="n">
         <v>0</v>
@@ -36078,10 +36078,10 @@
         <v>0.001206</v>
       </c>
       <c r="Y320" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z320" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA320" s="3" t="n">
         <v>0</v>
@@ -36278,7 +36278,7 @@
         <v>0.000821</v>
       </c>
       <c r="Y322" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z322" s="3" t="n">
         <v>0</v>
@@ -36481,7 +36481,7 @@
         <v>0</v>
       </c>
       <c r="Z324" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA324" s="3" t="n">
         <v>0</v>
@@ -37078,10 +37078,10 @@
         <v>0.0007649999999999999</v>
       </c>
       <c r="Y330" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z330" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA330" s="3" t="n">
         <v>0</v>
@@ -37678,7 +37678,7 @@
         <v>0.001217</v>
       </c>
       <c r="Y336" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z336" s="3" t="n">
         <v>-0</v>
@@ -37878,10 +37878,10 @@
         <v>0.001205</v>
       </c>
       <c r="Y338" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z338" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA338" s="3" t="n">
         <v>0</v>
@@ -38078,7 +38078,7 @@
         <v>0.001199</v>
       </c>
       <c r="Y340" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z340" s="3" t="n">
         <v>-0</v>
@@ -38278,10 +38278,10 @@
         <v>0.000727</v>
       </c>
       <c r="Y342" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z342" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA342" s="3" t="n">
         <v>1</v>
@@ -38481,7 +38481,7 @@
         <v>0</v>
       </c>
       <c r="Z344" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA344" s="3" t="n">
         <v>0</v>
@@ -38678,10 +38678,10 @@
         <v>0.000592</v>
       </c>
       <c r="Y346" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z346" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA346" s="3" t="n">
         <v>0</v>
@@ -39178,7 +39178,7 @@
         <v>0.000518</v>
       </c>
       <c r="Y351" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z351" s="3" t="n">
         <v>0</v>
@@ -39454,10 +39454,10 @@
         <v>0.531477</v>
       </c>
       <c r="Y355" s="3" t="n">
-        <v>0.212902</v>
+        <v>0.116944</v>
       </c>
       <c r="Z355" s="3" t="n">
-        <v>0.154979</v>
+        <v>0.096067</v>
       </c>
       <c r="AB355" s="3" t="n">
         <v>0.636927</v>
@@ -39516,10 +39516,10 @@
         <v>0.44762</v>
       </c>
       <c r="Y357" s="3" t="n">
-        <v>0.409183</v>
+        <v>0.358207</v>
       </c>
       <c r="Z357" s="3" t="n">
-        <v>0.383337</v>
+        <v>0.372864</v>
       </c>
       <c r="AA357" s="3" t="n">
         <v>0.556443</v>
@@ -39641,7 +39641,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -39652,6 +39652,8 @@
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -39682,15 +39684,25 @@
       </c>
       <c r="F1" s="4" t="inlineStr">
         <is>
+          <t>Pearson_partial_r</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Spearman_partial_rho</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
           <t>Recall</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="I1" s="4" t="inlineStr">
         <is>
           <t>Precision</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="J1" s="4" t="inlineStr">
         <is>
           <t>F1</t>
         </is>
@@ -39717,12 +39729,18 @@
         <v>0.414502</v>
       </c>
       <c r="F2" t="n">
+        <v>0.08426699999999999</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.055204</v>
+      </c>
+      <c r="H2" t="n">
         <v>0.7386363636363636</v>
       </c>
-      <c r="G2" t="n">
+      <c r="I2" t="n">
         <v>0.5508474576271186</v>
       </c>
-      <c r="H2" t="n">
+      <c r="J2" t="n">
         <v>0.6310679611650486</v>
       </c>
     </row>
@@ -39747,12 +39765,18 @@
         <v>0.482882</v>
       </c>
       <c r="F3" t="n">
+        <v>0.232888</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.082041</v>
+      </c>
+      <c r="H3" t="n">
         <v>0.6222222222222222</v>
       </c>
-      <c r="G3" t="n">
+      <c r="I3" t="n">
         <v>0.711864406779661</v>
       </c>
-      <c r="H3" t="n">
+      <c r="J3" t="n">
         <v>0.6640316205533597</v>
       </c>
     </row>
@@ -39777,12 +39801,18 @@
         <v>0.282294</v>
       </c>
       <c r="F4" t="n">
+        <v>-0.058886</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-0.028472</v>
+      </c>
+      <c r="H4" t="n">
         <v>0.696969696969697</v>
       </c>
-      <c r="G4" t="n">
+      <c r="I4" t="n">
         <v>0.3898305084745763</v>
       </c>
-      <c r="H4" t="n">
+      <c r="J4" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -39807,12 +39837,18 @@
         <v>0.326574</v>
       </c>
       <c r="F5" t="n">
+        <v>0.062137</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.029295</v>
+      </c>
+      <c r="H5" t="n">
         <v>0.6136363636363636</v>
       </c>
-      <c r="G5" t="n">
+      <c r="I5" t="n">
         <v>0.5142857142857142</v>
       </c>
-      <c r="H5" t="n">
+      <c r="J5" t="n">
         <v>0.5595854922279793</v>
       </c>
     </row>
@@ -39837,12 +39873,18 @@
         <v>0.38949</v>
       </c>
       <c r="F6" t="n">
+        <v>0.191857</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.08333400000000001</v>
+      </c>
+      <c r="H6" t="n">
         <v>0.5185185185185185</v>
       </c>
-      <c r="G6" t="n">
+      <c r="I6" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="H6" t="n">
+      <c r="J6" t="n">
         <v>0.5833333333333334</v>
       </c>
     </row>
@@ -39867,12 +39909,18 @@
         <v>0.214899</v>
       </c>
       <c r="F7" t="n">
+        <v>-0.044173</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-0.039888</v>
+      </c>
+      <c r="H7" t="n">
         <v>0.5606060606060606</v>
       </c>
-      <c r="G7" t="n">
+      <c r="I7" t="n">
         <v>0.3523809523809524</v>
       </c>
-      <c r="H7" t="n">
+      <c r="J7" t="n">
         <v>0.4327485380116959</v>
       </c>
     </row>
@@ -39891,18 +39939,24 @@
         <v>0.386366</v>
       </c>
       <c r="D8" t="n">
-        <v>0.409183</v>
+        <v>0.358207</v>
       </c>
       <c r="E8" t="n">
-        <v>0.315081</v>
+        <v>0.278041</v>
       </c>
       <c r="F8" t="n">
+        <v>0.143097</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.164527</v>
+      </c>
+      <c r="H8" t="n">
         <v>0.2954545454545455</v>
       </c>
-      <c r="G8" t="n">
+      <c r="I8" t="n">
         <v>1</v>
       </c>
-      <c r="H8" t="n">
+      <c r="J8" t="n">
         <v>0.456140350877193</v>
       </c>
     </row>
@@ -39921,18 +39975,24 @@
         <v>0.21634</v>
       </c>
       <c r="D9" t="n">
-        <v>0.212902</v>
+        <v>0.116944</v>
       </c>
       <c r="E9" t="n">
-        <v>0.160366</v>
+        <v>0.09010600000000001</v>
       </c>
       <c r="F9" t="n">
+        <v>0.055515</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-0.269918</v>
+      </c>
+      <c r="H9" t="n">
         <v>0.162962962962963</v>
       </c>
-      <c r="G9" t="n">
+      <c r="I9" t="n">
         <v>0.8461538461538461</v>
       </c>
-      <c r="H9" t="n">
+      <c r="J9" t="n">
         <v>0.2732919254658385</v>
       </c>
     </row>
@@ -39951,18 +40011,24 @@
         <v>0.418566</v>
       </c>
       <c r="D10" t="n">
-        <v>0.371064</v>
+        <v>0.322998</v>
       </c>
       <c r="E10" t="n">
-        <v>0.301812</v>
+        <v>0.261421</v>
       </c>
       <c r="F10" t="n">
+        <v>0.345677</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.185114</v>
+      </c>
+      <c r="H10" t="n">
         <v>0.3636363636363636</v>
       </c>
-      <c r="G10" t="n">
+      <c r="I10" t="n">
         <v>0.9230769230769231</v>
       </c>
-      <c r="H10" t="n">
+      <c r="J10" t="n">
         <v>0.5217391304347827</v>
       </c>
     </row>
@@ -39981,18 +40047,24 @@
         <v>0.397306</v>
       </c>
       <c r="D11" t="n">
-        <v>0.383337</v>
+        <v>0.372864</v>
       </c>
       <c r="E11" t="n">
-        <v>0.2857</v>
+        <v>0.283471</v>
       </c>
       <c r="F11" t="n">
+        <v>0.15142</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.198956</v>
+      </c>
+      <c r="H11" t="n">
         <v>0.3295454545454545</v>
       </c>
-      <c r="G11" t="n">
+      <c r="I11" t="n">
         <v>1</v>
       </c>
-      <c r="H11" t="n">
+      <c r="J11" t="n">
         <v>0.4957264957264957</v>
       </c>
     </row>
@@ -40011,18 +40083,24 @@
         <v>0.218819</v>
       </c>
       <c r="D12" t="n">
-        <v>0.154979</v>
+        <v>0.096067</v>
       </c>
       <c r="E12" t="n">
-        <v>0.111336</v>
+        <v>0.071954</v>
       </c>
       <c r="F12" t="n">
+        <v>0.050942</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-0.284299</v>
+      </c>
+      <c r="H12" t="n">
         <v>0.1703703703703704</v>
       </c>
-      <c r="G12" t="n">
+      <c r="I12" t="n">
         <v>0.7931034482758621</v>
       </c>
-      <c r="H12" t="n">
+      <c r="J12" t="n">
         <v>0.2804878048780488</v>
       </c>
     </row>
@@ -40041,18 +40119,24 @@
         <v>0.437514</v>
       </c>
       <c r="D13" t="n">
-        <v>0.375819</v>
+        <v>0.333558</v>
       </c>
       <c r="E13" t="n">
-        <v>0.306257</v>
+        <v>0.271209</v>
       </c>
       <c r="F13" t="n">
+        <v>0.364928</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.205095</v>
+      </c>
+      <c r="H13" t="n">
         <v>0.3939393939393939</v>
       </c>
-      <c r="G13" t="n">
+      <c r="I13" t="n">
         <v>0.896551724137931</v>
       </c>
-      <c r="H13" t="n">
+      <c r="J13" t="n">
         <v>0.5473684210526315</v>
       </c>
     </row>
@@ -40077,12 +40161,18 @@
         <v>0.5249200000000001</v>
       </c>
       <c r="F14" t="n">
+        <v/>
+      </c>
+      <c r="G14" t="n">
+        <v/>
+      </c>
+      <c r="H14" t="n">
         <v>0.7840909090909091</v>
       </c>
-      <c r="G14" t="n">
+      <c r="I14" t="n">
         <v>0.6764705882352942</v>
       </c>
-      <c r="H14" t="n">
+      <c r="J14" t="n">
         <v>0.7263157894736842</v>
       </c>
     </row>
@@ -40107,12 +40197,18 @@
         <v>0.603083</v>
       </c>
       <c r="F15" t="n">
+        <v/>
+      </c>
+      <c r="G15" t="n">
+        <v/>
+      </c>
+      <c r="H15" t="n">
         <v>0.6148148148148148</v>
       </c>
-      <c r="G15" t="n">
+      <c r="I15" t="n">
         <v>0.8137254901960784</v>
       </c>
-      <c r="H15" t="n">
+      <c r="J15" t="n">
         <v>0.70042194092827</v>
       </c>
     </row>
@@ -40137,12 +40233,18 @@
         <v>0.382877</v>
       </c>
       <c r="F16" t="n">
+        <v/>
+      </c>
+      <c r="G16" t="n">
+        <v/>
+      </c>
+      <c r="H16" t="n">
         <v>0.696969696969697</v>
       </c>
-      <c r="G16" t="n">
+      <c r="I16" t="n">
         <v>0.4509803921568628</v>
       </c>
-      <c r="H16" t="n">
+      <c r="J16" t="n">
         <v>0.5476190476190477</v>
       </c>
     </row>
